--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-09-11</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-09-11</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-09-11</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-09-11</t>
+    <t>Price_2026-09-18</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-09-18</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-09-18</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-09-18</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-09-18</t>
   </si>
   <si>
     <t>RS_Score_2026-09-11</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-08-28</t>
   </si>
   <si>
-    <t>RS_Score_2026-08-21</t>
-  </si>
-  <si>
     <t>ETERNAL</t>
   </si>
   <si>
     <t>KOTAKBANK</t>
   </si>
   <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
     <t>TITAN</t>
   </si>
   <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
-    <t>GRASIM</t>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
   </si>
   <si>
     <t>JSWSTEEL</t>
   </si>
   <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
+    <t>SBIN</t>
   </si>
   <si>
     <t>ICICIBANK</t>
   </si>
   <si>
-    <t>BAJFINANCE</t>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
   </si>
   <si>
     <t>BAJAJFINSV</t>
   </si>
   <si>
-    <t>MAXHEALTH</t>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
   </si>
   <si>
     <t>HINDALCO</t>
   </si>
   <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
   </si>
   <si>
     <t>TCS</t>
   </si>
   <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>ONGC</t>
   </si>
   <si>
     <t>NTPC</t>
   </si>
   <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>ITC</t>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>TMPV</t>
   </si>
   <si>
     <t>WIPRO</t>
   </si>
   <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
     <t>MARUTI</t>
   </si>
   <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
     <t>2026-09-11</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>323.5</v>
+        <v>326.85</v>
       </c>
       <c r="C2" s="2">
-        <v>31.57</v>
+        <v>35.4</v>
       </c>
       <c r="D2" s="2">
-        <v>14.15</v>
+        <v>14.6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.73</v>
+        <v>-0.09</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>419</v>
+        <v>416.5</v>
       </c>
       <c r="C3" s="2">
-        <v>10.15</v>
+        <v>6.49</v>
       </c>
       <c r="D3" s="2">
-        <v>10.08</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E3" s="2">
-        <v>6.7</v>
+        <v>3.75</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>96</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>90</v>
-      </c>
-      <c r="I3" s="2">
-        <v>70</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>11768</v>
+        <v>1824</v>
       </c>
       <c r="C4" s="2">
-        <v>12.63</v>
+        <v>2.46</v>
       </c>
       <c r="D4" s="2">
-        <v>17.25</v>
+        <v>0.76</v>
       </c>
       <c r="E4" s="2">
-        <v>0.9</v>
+        <v>9.08</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,16 +818,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5009.5</v>
+        <v>11414</v>
       </c>
       <c r="C5" s="2">
-        <v>19.51</v>
+        <v>13.49</v>
       </c>
       <c r="D5" s="2">
-        <v>12.08</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E5" s="2">
-        <v>-1.16</v>
+        <v>-3.27</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
@@ -836,7 +836,7 @@
         <v>94</v>
       </c>
       <c r="H5" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
         <v>96</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>3060</v>
+        <v>8768.5</v>
       </c>
       <c r="C6" s="2">
-        <v>22.44</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D6" s="2">
-        <v>-4.57</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" s="2">
-        <v>1.75</v>
+        <v>0.76</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="I6" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>3319</v>
+        <v>4798.5</v>
       </c>
       <c r="C7" s="2">
-        <v>11.57</v>
+        <v>15.46</v>
       </c>
       <c r="D7" s="2">
-        <v>3.62</v>
+        <v>4.28</v>
       </c>
       <c r="E7" s="2">
-        <v>2.11</v>
+        <v>-5.52</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I7" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1304</v>
+        <v>1040.3</v>
       </c>
       <c r="C8" s="2">
-        <v>3.87</v>
+        <v>13.64</v>
       </c>
       <c r="D8" s="2">
-        <v>5.49</v>
+        <v>1.73</v>
       </c>
       <c r="E8" s="2">
-        <v>2.05</v>
+        <v>-3.41</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I8" s="2">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>8900</v>
+        <v>1537.1</v>
       </c>
       <c r="C9" s="2">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="D9" s="2">
-        <v>0.25</v>
+        <v>2.17</v>
       </c>
       <c r="E9" s="2">
-        <v>0.84</v>
+        <v>-2.96</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1541</v>
+        <v>1049.3</v>
       </c>
       <c r="C10" s="2">
-        <v>8.48</v>
+        <v>-0.7</v>
       </c>
       <c r="D10" s="2">
-        <v>9.56</v>
+        <v>-5.14</v>
       </c>
       <c r="E10" s="2">
-        <v>-4.29</v>
+        <v>5.94</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H10" s="2">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="I10" s="2">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>426.4</v>
+        <v>3187</v>
       </c>
       <c r="C11" s="2">
-        <v>-5.79</v>
+        <v>8.6</v>
       </c>
       <c r="D11" s="2">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="E11" s="2">
-        <v>5.72</v>
+        <v>-3.07</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="I11" s="2">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1764.6</v>
+        <v>1249.3</v>
       </c>
       <c r="C12" s="2">
-        <v>0.27</v>
+        <v>10.07</v>
       </c>
       <c r="D12" s="2">
-        <v>-5.35</v>
+        <v>3.35</v>
       </c>
       <c r="E12" s="2">
-        <v>4.35</v>
+        <v>-5.5</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H12" s="2">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="I12" s="2">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1379.3</v>
+        <v>7516</v>
       </c>
       <c r="C13" s="2">
-        <v>9.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D13" s="2">
-        <v>-2.52</v>
+        <v>4.09</v>
       </c>
       <c r="E13" s="2">
-        <v>-2.54</v>
+        <v>-6.6</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H13" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I13" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1034.5</v>
+        <v>418</v>
       </c>
       <c r="C14" s="2">
-        <v>11.2</v>
+        <v>-7.17</v>
       </c>
       <c r="D14" s="2">
-        <v>0.52</v>
+        <v>-0.29</v>
       </c>
       <c r="E14" s="2">
-        <v>-5.03</v>
+        <v>4.03</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="I14" s="2">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1913.5</v>
+        <v>1257</v>
       </c>
       <c r="C15" s="2">
-        <v>6.74</v>
+        <v>1.62</v>
       </c>
       <c r="D15" s="2">
-        <v>2.29</v>
+        <v>-4.73</v>
       </c>
       <c r="E15" s="2">
-        <v>-4.56</v>
+        <v>1.7</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H15" s="2">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I15" s="2">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>1038.6</v>
+        <v>2923.2</v>
       </c>
       <c r="C16" s="2">
-        <v>0.24</v>
+        <v>8.73</v>
       </c>
       <c r="D16" s="2">
-        <v>-8.289999999999999</v>
+        <v>-8</v>
       </c>
       <c r="E16" s="2">
-        <v>3.48</v>
+        <v>-2.51</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="I16" s="2">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1014</v>
+        <v>1893.3</v>
       </c>
       <c r="C17" s="2">
-        <v>-0.41</v>
+        <v>-1.08</v>
       </c>
       <c r="D17" s="2">
-        <v>3.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E17" s="2">
-        <v>-3.42</v>
+        <v>-2.16</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H17" s="2">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="I17" s="2">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>4973</v>
+        <v>4845</v>
       </c>
       <c r="C18" s="2">
-        <v>15.67</v>
+        <v>13.31</v>
       </c>
       <c r="D18" s="2">
-        <v>-8.050000000000001</v>
+        <v>-7.35</v>
       </c>
       <c r="E18" s="2">
-        <v>-5.73</v>
+        <v>-5.28</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H18" s="2">
         <v>64</v>
       </c>
       <c r="I18" s="2">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1861</v>
+        <v>1275.6</v>
       </c>
       <c r="C19" s="2">
-        <v>-0.36</v>
+        <v>-0.76</v>
       </c>
       <c r="D19" s="2">
-        <v>-2.45</v>
+        <v>3.09</v>
       </c>
       <c r="E19" s="2">
-        <v>-1.12</v>
+        <v>-3.87</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
+        <v>76</v>
+      </c>
+      <c r="H19" s="2">
+        <v>84</v>
+      </c>
+      <c r="I19" s="2">
         <v>74</v>
-      </c>
-      <c r="H19" s="2">
-        <v>68</v>
-      </c>
-      <c r="I19" s="2">
-        <v>64</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>7530</v>
+        <v>996.2</v>
       </c>
       <c r="C20" s="2">
-        <v>5.64</v>
+        <v>6.05</v>
       </c>
       <c r="D20" s="2">
-        <v>1.84</v>
+        <v>-3.93</v>
       </c>
       <c r="E20" s="2">
-        <v>-6.46</v>
+        <v>-4.17</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="I20" s="2">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1246</v>
+        <v>1338.9</v>
       </c>
       <c r="C21" s="2">
-        <v>-1.99</v>
+        <v>7.92</v>
       </c>
       <c r="D21" s="2">
-        <v>-6.92</v>
+        <v>-4.21</v>
       </c>
       <c r="E21" s="2">
-        <v>1.52</v>
+        <v>-5.38</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H21" s="2">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="I21" s="2">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>2200.8</v>
+        <v>2789</v>
       </c>
       <c r="C22" s="2">
-        <v>-6.27</v>
+        <v>3.9</v>
       </c>
       <c r="D22" s="2">
-        <v>7.55</v>
+        <v>-3.83</v>
       </c>
       <c r="E22" s="2">
-        <v>-4.86</v>
+        <v>-3.99</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="H22" s="2">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="I22" s="2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1206.1</v>
+        <v>1867.3</v>
       </c>
       <c r="C23" s="2">
-        <v>1.97</v>
+        <v>-1.76</v>
       </c>
       <c r="D23" s="2">
-        <v>7.42</v>
+        <v>-2.82</v>
       </c>
       <c r="E23" s="2">
-        <v>-8.970000000000001</v>
+        <v>-2.24</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H23" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I23" s="2">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>3930.7</v>
+        <v>1766.9</v>
       </c>
       <c r="C24" s="2">
-        <v>0.73</v>
+        <v>-5.03</v>
       </c>
       <c r="D24" s="2">
-        <v>-2.73</v>
+        <v>-4.8</v>
       </c>
       <c r="E24" s="2">
-        <v>-3.82</v>
+        <v>0.29</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H24" s="2">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I24" s="2">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1366</v>
+        <v>1394.5</v>
       </c>
       <c r="C25" s="2">
-        <v>5.66</v>
+        <v>-1.31</v>
       </c>
       <c r="D25" s="2">
-        <v>-7.22</v>
+        <v>-2.26</v>
       </c>
       <c r="E25" s="2">
-        <v>-4.58</v>
+        <v>-3.02</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
+        <v>56</v>
+      </c>
+      <c r="H25" s="2">
         <v>40</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="2">
         <v>62</v>
-      </c>
-      <c r="I25" s="2">
-        <v>78</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>995.7</v>
+        <v>3885</v>
       </c>
       <c r="C26" s="2">
-        <v>4.11</v>
+        <v>0.13</v>
       </c>
       <c r="D26" s="2">
-        <v>-4.05</v>
+        <v>-1.11</v>
       </c>
       <c r="E26" s="2">
-        <v>-6.17</v>
+        <v>-5.01</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H26" s="2">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I26" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1831.1</v>
+        <v>185.54</v>
       </c>
       <c r="C27" s="2">
-        <v>5.36</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="D27" s="2">
-        <v>-3.72</v>
+        <v>-0.84</v>
       </c>
       <c r="E27" s="2">
-        <v>-7.02</v>
+        <v>-0.41</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="H27" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I27" s="2">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1028.6</v>
+        <v>1852.5</v>
       </c>
       <c r="C28" s="2">
-        <v>5.99</v>
+        <v>5.76</v>
       </c>
       <c r="D28" s="2">
-        <v>-3.17</v>
+        <v>-2.91</v>
       </c>
       <c r="E28" s="2">
-        <v>-8.32</v>
+        <v>-7.45</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="H28" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I28" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>404.35</v>
+        <v>550.95</v>
       </c>
       <c r="C29" s="2">
-        <v>-6.26</v>
+        <v>-8.6</v>
       </c>
       <c r="D29" s="2">
-        <v>-4.85</v>
+        <v>-3.92</v>
       </c>
       <c r="E29" s="2">
-        <v>-1.96</v>
+        <v>-0.36</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H29" s="2">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="I29" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>269.1</v>
+        <v>731</v>
       </c>
       <c r="C30" s="2">
-        <v>-13.44</v>
+        <v>-3.33</v>
       </c>
       <c r="D30" s="2">
-        <v>-5.71</v>
+        <v>-10.63</v>
       </c>
       <c r="E30" s="2">
-        <v>1.11</v>
+        <v>0.27</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H30" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I30" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>183</v>
+        <v>11014</v>
       </c>
       <c r="C31" s="2">
-        <v>-11.93</v>
+        <v>-2.79</v>
       </c>
       <c r="D31" s="2">
-        <v>-4.12</v>
+        <v>-2.87</v>
       </c>
       <c r="E31" s="2">
-        <v>-1.61</v>
+        <v>-4.26</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H31" s="2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I31" s="2">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>333.4</v>
+        <v>1010</v>
       </c>
       <c r="C32" s="2">
-        <v>-14.24</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="D32" s="2">
-        <v>-5.4</v>
+        <v>-3.64</v>
       </c>
       <c r="E32" s="2">
-        <v>0</v>
+        <v>-9.74</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="I32" s="2">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>11000</v>
+        <v>270.3</v>
       </c>
       <c r="C33" s="2">
-        <v>-5.41</v>
+        <v>-8.85</v>
       </c>
       <c r="D33" s="2">
-        <v>-3.74</v>
+        <v>-5.49</v>
       </c>
       <c r="E33" s="2">
-        <v>-5.83</v>
+        <v>-0.41</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="I33" s="2">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1257.5</v>
+        <v>1185</v>
       </c>
       <c r="C34" s="2">
-        <v>-9</v>
+        <v>-10.42</v>
       </c>
       <c r="D34" s="2">
-        <v>-4.83</v>
+        <v>-4.01</v>
       </c>
       <c r="E34" s="2">
-        <v>-4.45</v>
+        <v>-0.42</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I34" s="2">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,16 +1778,16 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1386.2</v>
+        <v>229.89</v>
       </c>
       <c r="C35" s="2">
-        <v>-6.01</v>
+        <v>-0.95</v>
       </c>
       <c r="D35" s="2">
-        <v>-5.49</v>
+        <v>-4.55</v>
       </c>
       <c r="E35" s="2">
-        <v>-5.7</v>
+        <v>-5</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
@@ -1796,10 +1796,10 @@
         <v>30</v>
       </c>
       <c r="H35" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I35" s="2">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>3107</v>
+        <v>393.3</v>
       </c>
       <c r="C36" s="2">
-        <v>-3.27</v>
+        <v>-7.68</v>
       </c>
       <c r="D36" s="2">
-        <v>-2.94</v>
+        <v>-4.13</v>
       </c>
       <c r="E36" s="2">
-        <v>-8.359999999999999</v>
+        <v>-3.84</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H36" s="2">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="I36" s="2">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,25 +1842,25 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>2818.7</v>
+        <v>1372.4</v>
       </c>
       <c r="C37" s="2">
-        <v>1.27</v>
+        <v>-3.68</v>
       </c>
       <c r="D37" s="2">
-        <v>-15.7</v>
+        <v>-3.83</v>
       </c>
       <c r="E37" s="2">
-        <v>-4.32</v>
+        <v>-6.72</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H37" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I37" s="2">
         <v>50</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>229.9</v>
+        <v>972.7</v>
       </c>
       <c r="C38" s="2">
-        <v>-4.12</v>
+        <v>-7.15</v>
       </c>
       <c r="D38" s="2">
-        <v>-3.98</v>
+        <v>0.61</v>
       </c>
       <c r="E38" s="2">
-        <v>-7.95</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="I38" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>1700.6</v>
+        <v>1051.4</v>
       </c>
       <c r="C39" s="2">
-        <v>-9.75</v>
+        <v>-5.98</v>
       </c>
       <c r="D39" s="2">
-        <v>-4.87</v>
+        <v>-4.64</v>
       </c>
       <c r="E39" s="2">
-        <v>-5.02</v>
+        <v>-6.96</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="H39" s="2">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="I39" s="2">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>232.5</v>
+        <v>3052</v>
       </c>
       <c r="C40" s="2">
-        <v>-16.91</v>
+        <v>0.01</v>
       </c>
       <c r="D40" s="2">
-        <v>-4.27</v>
+        <v>-3.43</v>
       </c>
       <c r="E40" s="2">
-        <v>-2.1</v>
+        <v>-10.61</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H40" s="2">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="I40" s="2">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>530</v>
+        <v>2105</v>
       </c>
       <c r="C41" s="2">
-        <v>-14.58</v>
+        <v>-6.04</v>
       </c>
       <c r="D41" s="2">
-        <v>-6.06</v>
+        <v>-2.98</v>
       </c>
       <c r="E41" s="2">
-        <v>-2.39</v>
+        <v>-7.84</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H41" s="2">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="I41" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>708.25</v>
+        <v>262.3</v>
       </c>
       <c r="C42" s="2">
-        <v>-5.72</v>
+        <v>-13.12</v>
       </c>
       <c r="D42" s="2">
-        <v>-14.65</v>
+        <v>-6.2</v>
       </c>
       <c r="E42" s="2">
-        <v>-2.85</v>
+        <v>-2.74</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H42" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I42" s="2">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1165.5</v>
+        <v>1226.4</v>
       </c>
       <c r="C43" s="2">
-        <v>-8.359999999999999</v>
+        <v>-7.77</v>
       </c>
       <c r="D43" s="2">
-        <v>-14.26</v>
+        <v>-5.44</v>
       </c>
       <c r="E43" s="2">
-        <v>-2.22</v>
+        <v>-6.37</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H43" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I43" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1037.7</v>
+        <v>2451.3</v>
       </c>
       <c r="C44" s="2">
-        <v>-9.93</v>
+        <v>-5.41</v>
       </c>
       <c r="D44" s="2">
-        <v>-0.43</v>
+        <v>-7.57</v>
       </c>
       <c r="E44" s="2">
-        <v>-8.970000000000001</v>
+        <v>-7.18</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="H44" s="2">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="I44" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>2472.5</v>
+        <v>232.8</v>
       </c>
       <c r="C45" s="2">
-        <v>-2.81</v>
+        <v>-21.34</v>
       </c>
       <c r="D45" s="2">
-        <v>-10.25</v>
+        <v>-5.9</v>
       </c>
       <c r="E45" s="2">
-        <v>-8</v>
+        <v>-1.17</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H45" s="2">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I45" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>259.85</v>
+        <v>323.65</v>
       </c>
       <c r="C46" s="2">
-        <v>-12.73</v>
+        <v>-15.75</v>
       </c>
       <c r="D46" s="2">
-        <v>-9.85</v>
+        <v>-6.99</v>
       </c>
       <c r="E46" s="2">
-        <v>-4.83</v>
+        <v>-3.64</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H46" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I46" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>167.4</v>
+        <v>1942.2</v>
       </c>
       <c r="C47" s="2">
-        <v>-13.92</v>
+        <v>-12.96</v>
       </c>
       <c r="D47" s="2">
-        <v>-2.87</v>
+        <v>-8.84</v>
       </c>
       <c r="E47" s="2">
-        <v>-7.97</v>
+        <v>-4.33</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H47" s="2">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I47" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>12590</v>
+        <v>303.8</v>
       </c>
       <c r="C48" s="2">
-        <v>-5.69</v>
+        <v>-13.26</v>
       </c>
       <c r="D48" s="2">
-        <v>-12.03</v>
+        <v>-11.23</v>
       </c>
       <c r="E48" s="2">
-        <v>-8.5</v>
+        <v>-3.37</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H48" s="2">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="I48" s="2">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>1927</v>
+        <v>166.83</v>
       </c>
       <c r="C49" s="2">
-        <v>-15.63</v>
+        <v>-12.19</v>
       </c>
       <c r="D49" s="2">
-        <v>-12.49</v>
+        <v>-5.43</v>
       </c>
       <c r="E49" s="2">
-        <v>-6.23</v>
+        <v>-7.99</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H49" s="2">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="I49" s="2">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>301.1</v>
+        <v>1013.7</v>
       </c>
       <c r="C50" s="2">
-        <v>-12.25</v>
+        <v>-16.96</v>
       </c>
       <c r="D50" s="2">
-        <v>-13.24</v>
+        <v>-7.73</v>
       </c>
       <c r="E50" s="2">
-        <v>-8.81</v>
+        <v>-4.59</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H50" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I50" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>991</v>
+        <v>12103</v>
       </c>
       <c r="C51" s="2">
-        <v>-21.37</v>
+        <v>-6.08</v>
       </c>
       <c r="D51" s="2">
-        <v>-11.35</v>
+        <v>-10.74</v>
       </c>
       <c r="E51" s="2">
-        <v>-7.61</v>
+        <v>-11.14</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H51" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I51" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>323.5</v>
+        <v>326.85</v>
       </c>
       <c r="C2" s="2">
-        <v>31.57</v>
+        <v>35.4</v>
       </c>
       <c r="D2" s="2">
-        <v>14.15</v>
+        <v>14.6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.73</v>
+        <v>-0.09</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2488,22 +2488,22 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>11768</v>
+        <v>416.5</v>
       </c>
       <c r="C3" s="2">
-        <v>12.63</v>
+        <v>6.49</v>
       </c>
       <c r="D3" s="2">
-        <v>17.25</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E3" s="2">
-        <v>0.9</v>
+        <v>3.75</v>
       </c>
       <c r="F3" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G3" s="2">
         <v>98</v>
@@ -2512,7 +2512,7 @@
         <v>96</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2520,16 +2520,16 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>5009.5</v>
+        <v>11414</v>
       </c>
       <c r="C4" s="2">
-        <v>19.51</v>
+        <v>13.49</v>
       </c>
       <c r="D4" s="2">
-        <v>12.08</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E4" s="2">
-        <v>-1.16</v>
+        <v>-3.27</v>
       </c>
       <c r="F4" s="2">
         <v>94</v>
@@ -2538,7 +2538,7 @@
         <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
         <v>96</v>
@@ -2549,32 +2549,90 @@
         <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>3319</v>
+        <v>4798.5</v>
       </c>
       <c r="C5" s="2">
-        <v>11.57</v>
+        <v>15.46</v>
       </c>
       <c r="D5" s="2">
-        <v>3.62</v>
+        <v>4.28</v>
       </c>
       <c r="E5" s="2">
-        <v>2.11</v>
+        <v>-5.52</v>
       </c>
       <c r="F5" s="2">
         <v>90</v>
       </c>
       <c r="G5" s="2">
+        <v>96</v>
+      </c>
+      <c r="H5" s="2">
+        <v>94</v>
+      </c>
+      <c r="I5" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1537.1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>10.28</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-2.96</v>
+      </c>
+      <c r="F6" s="2">
+        <v>86</v>
+      </c>
+      <c r="G6" s="2">
+        <v>88</v>
+      </c>
+      <c r="H6" s="2">
+        <v>90</v>
+      </c>
+      <c r="I6" s="2">
         <v>92</v>
       </c>
-      <c r="H5" s="2">
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3187</v>
+      </c>
+      <c r="C7" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1.67</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-3.07</v>
+      </c>
+      <c r="F7" s="2">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2">
+        <v>90</v>
+      </c>
+      <c r="H7" s="2">
+        <v>92</v>
+      </c>
+      <c r="I7" s="2">
         <v>88</v>
       </c>
-      <c r="I5" s="2">
-        <v>88</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2582,7 +2640,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2590,7 +2648,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2598,22 +2656,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2624,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2666,16 +2724,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>323.5</v>
+        <v>326.85</v>
       </c>
       <c r="C2" s="2">
-        <v>31.57</v>
+        <v>35.4</v>
       </c>
       <c r="D2" s="2">
-        <v>14.15</v>
+        <v>14.6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.73</v>
+        <v>-0.09</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2695,28 +2753,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>419</v>
+        <v>416.5</v>
       </c>
       <c r="C3" s="2">
-        <v>10.15</v>
+        <v>6.49</v>
       </c>
       <c r="D3" s="2">
-        <v>10.08</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E3" s="2">
-        <v>6.7</v>
+        <v>3.75</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>96</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>90</v>
-      </c>
-      <c r="I3" s="2">
-        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2724,28 +2782,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>11768</v>
+        <v>1824</v>
       </c>
       <c r="C4" s="2">
-        <v>12.63</v>
+        <v>2.46</v>
       </c>
       <c r="D4" s="2">
-        <v>17.25</v>
+        <v>0.76</v>
       </c>
       <c r="E4" s="2">
-        <v>0.9</v>
+        <v>9.08</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2753,16 +2811,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5009.5</v>
+        <v>11414</v>
       </c>
       <c r="C5" s="2">
-        <v>19.51</v>
+        <v>13.49</v>
       </c>
       <c r="D5" s="2">
-        <v>12.08</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E5" s="2">
-        <v>-1.16</v>
+        <v>-3.27</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
@@ -2771,7 +2829,7 @@
         <v>94</v>
       </c>
       <c r="H5" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
         <v>96</v>
@@ -2779,93 +2837,122 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>3319</v>
+        <v>8768.5</v>
       </c>
       <c r="C6" s="2">
-        <v>11.57</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D6" s="2">
-        <v>3.62</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" s="2">
-        <v>2.11</v>
+        <v>0.76</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I6" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1304</v>
+        <v>4798.5</v>
       </c>
       <c r="C7" s="2">
-        <v>3.87</v>
+        <v>15.46</v>
       </c>
       <c r="D7" s="2">
-        <v>5.49</v>
+        <v>4.28</v>
       </c>
       <c r="E7" s="2">
-        <v>2.05</v>
+        <v>-5.52</v>
       </c>
       <c r="F7" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="I7" s="2">
-        <v>56</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>1541</v>
+        <v>1537.1</v>
       </c>
       <c r="C8" s="2">
-        <v>8.48</v>
+        <v>10.28</v>
       </c>
       <c r="D8" s="2">
-        <v>9.56</v>
+        <v>2.17</v>
       </c>
       <c r="E8" s="2">
-        <v>-4.29</v>
+        <v>-2.96</v>
       </c>
       <c r="F8" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2">
+        <v>88</v>
+      </c>
+      <c r="H8" s="2">
         <v>90</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>92</v>
       </c>
-      <c r="I8" s="2">
-        <v>74</v>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3187</v>
+      </c>
+      <c r="C9" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1.67</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-3.07</v>
+      </c>
+      <c r="F9" s="2">
+        <v>82</v>
+      </c>
+      <c r="G9" s="2">
+        <v>90</v>
+      </c>
+      <c r="H9" s="2">
+        <v>92</v>
+      </c>
+      <c r="I9" s="2">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2873,7 +2960,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2881,7 +2968,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2889,22 +2976,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2940,13 +3027,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2954,13 +3041,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2968,13 +3055,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2982,13 +3069,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-09-18</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-09-18</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-09-18</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-09-18</t>
+    <t>Price_2026-09-25</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-09-25</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-09-25</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-09-25</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-09-25</t>
   </si>
   <si>
     <t>RS_Score_2026-09-18</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-09-04</t>
   </si>
   <si>
-    <t>RS_Score_2026-08-28</t>
-  </si>
-  <si>
     <t>ETERNAL</t>
   </si>
   <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
     <t>KOTAKBANK</t>
   </si>
   <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>TITAN</t>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>ADANIENT</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
   </si>
   <si>
     <t>BAJFINANCE</t>
   </si>
   <si>
-    <t>TECHM</t>
+    <t>LT</t>
   </si>
   <si>
     <t>MAXHEALTH</t>
   </si>
   <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
   </si>
   <si>
     <t>EICHERMOT</t>
   </si>
   <si>
-    <t>COALINDIA</t>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>SBIN</t>
   </si>
   <si>
     <t>AXISBANK</t>
   </si>
   <si>
-    <t>ADANIENT</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>SBIN</t>
+    <t>M&amp;M</t>
   </si>
   <si>
     <t>ICICIBANK</t>
   </si>
   <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
     <t>TRENT</t>
   </si>
   <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
     <t>BAJAJFINSV</t>
   </si>
   <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>TCS</t>
   </si>
   <si>
     <t>INFY</t>
   </si>
   <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
     <t>TMPV</t>
   </si>
   <si>
     <t>WIPRO</t>
   </si>
   <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
     <t>2026-09-18</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>326.85</v>
+        <v>335</v>
       </c>
       <c r="C2" s="2">
-        <v>35.4</v>
+        <v>35.26</v>
       </c>
       <c r="D2" s="2">
-        <v>14.6</v>
+        <v>16.75</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.09</v>
+        <v>2.1</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,16 +754,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>416.5</v>
+        <v>1785.3</v>
       </c>
       <c r="C3" s="2">
-        <v>6.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D3" s="2">
-        <v>8.470000000000001</v>
+        <v>-3.18</v>
       </c>
       <c r="E3" s="2">
-        <v>3.75</v>
+        <v>12.06</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -772,10 +772,10 @@
         <v>98</v>
       </c>
       <c r="H3" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I3" s="2">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1824</v>
+        <v>4884</v>
       </c>
       <c r="C4" s="2">
-        <v>2.46</v>
+        <v>17.81</v>
       </c>
       <c r="D4" s="2">
-        <v>0.76</v>
+        <v>5.18</v>
       </c>
       <c r="E4" s="2">
-        <v>9.08</v>
+        <v>-4.28</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>11414</v>
+        <v>426.1</v>
       </c>
       <c r="C5" s="2">
-        <v>13.49</v>
+        <v>-4.53</v>
       </c>
       <c r="D5" s="2">
-        <v>9.949999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="E5" s="2">
-        <v>-3.27</v>
+        <v>7.4</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I5" s="2">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>8768.5</v>
+        <v>8889</v>
       </c>
       <c r="C6" s="2">
-        <v>9.449999999999999</v>
+        <v>5.89</v>
       </c>
       <c r="D6" s="2">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E6" s="2">
-        <v>0.76</v>
+        <v>-0.11</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
+        <v>96</v>
+      </c>
+      <c r="H6" s="2">
         <v>86</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>76</v>
-      </c>
-      <c r="I6" s="2">
-        <v>82</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>4798.5</v>
+        <v>1258</v>
       </c>
       <c r="C7" s="2">
-        <v>15.46</v>
+        <v>9.02</v>
       </c>
       <c r="D7" s="2">
-        <v>4.28</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2">
-        <v>-5.52</v>
+        <v>-4.13</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="I7" s="2">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1040.3</v>
+        <v>405</v>
       </c>
       <c r="C8" s="2">
-        <v>13.64</v>
+        <v>3.27</v>
       </c>
       <c r="D8" s="2">
-        <v>1.73</v>
+        <v>6.01</v>
       </c>
       <c r="E8" s="2">
-        <v>-3.41</v>
+        <v>-3.43</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I8" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1537.1</v>
+        <v>11208</v>
       </c>
       <c r="C9" s="2">
-        <v>10.28</v>
+        <v>8.34</v>
       </c>
       <c r="D9" s="2">
-        <v>2.17</v>
+        <v>6.51</v>
       </c>
       <c r="E9" s="2">
-        <v>-2.96</v>
+        <v>-7.6</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I9" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1049.3</v>
+        <v>1548</v>
       </c>
       <c r="C10" s="2">
-        <v>-0.7</v>
+        <v>10.64</v>
       </c>
       <c r="D10" s="2">
-        <v>-5.14</v>
+        <v>-1.8</v>
       </c>
       <c r="E10" s="2">
-        <v>5.94</v>
+        <v>-4.91</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H10" s="2">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="I10" s="2">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>3187</v>
+        <v>735.6</v>
       </c>
       <c r="C11" s="2">
-        <v>8.6</v>
+        <v>-4.97</v>
       </c>
       <c r="D11" s="2">
-        <v>1.67</v>
+        <v>-5.4</v>
       </c>
       <c r="E11" s="2">
-        <v>-3.07</v>
+        <v>3.75</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="H11" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="I11" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1249.3</v>
+        <v>1201</v>
       </c>
       <c r="C12" s="2">
-        <v>10.07</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="D12" s="2">
-        <v>3.35</v>
+        <v>-1.81</v>
       </c>
       <c r="E12" s="2">
-        <v>-5.5</v>
+        <v>4.04</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>7516</v>
+        <v>269</v>
       </c>
       <c r="C13" s="2">
-        <v>9.859999999999999</v>
+        <v>-9.09</v>
       </c>
       <c r="D13" s="2">
-        <v>4.09</v>
+        <v>-4.85</v>
       </c>
       <c r="E13" s="2">
-        <v>-6.6</v>
+        <v>5.28</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>418</v>
+        <v>1277</v>
       </c>
       <c r="C14" s="2">
-        <v>-7.17</v>
+        <v>-0.39</v>
       </c>
       <c r="D14" s="2">
-        <v>-0.29</v>
+        <v>1.59</v>
       </c>
       <c r="E14" s="2">
-        <v>4.03</v>
+        <v>-2.35</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
+        <v>66</v>
+      </c>
+      <c r="H14" s="2">
+        <v>76</v>
+      </c>
+      <c r="I14" s="2">
         <v>84</v>
-      </c>
-      <c r="H14" s="2">
-        <v>46</v>
-      </c>
-      <c r="I14" s="2">
-        <v>16</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1257</v>
+        <v>187.97</v>
       </c>
       <c r="C15" s="2">
-        <v>1.62</v>
+        <v>-8.74</v>
       </c>
       <c r="D15" s="2">
-        <v>-4.73</v>
+        <v>0.84</v>
       </c>
       <c r="E15" s="2">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H15" s="2">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="I15" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>2923.2</v>
+        <v>2900</v>
       </c>
       <c r="C16" s="2">
-        <v>8.73</v>
+        <v>1.81</v>
       </c>
       <c r="D16" s="2">
-        <v>-8</v>
+        <v>-8.9</v>
       </c>
       <c r="E16" s="2">
-        <v>-2.51</v>
+        <v>1.43</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2">
         <v>92</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <v>78</v>
-      </c>
-      <c r="I16" s="2">
-        <v>98</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1893.3</v>
+        <v>1399.7</v>
       </c>
       <c r="C17" s="2">
-        <v>-1.08</v>
+        <v>-0.08</v>
       </c>
       <c r="D17" s="2">
-        <v>0.8100000000000001</v>
+        <v>-2.91</v>
       </c>
       <c r="E17" s="2">
-        <v>-2.16</v>
+        <v>-0.67</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H17" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I17" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,25 +1234,25 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>4845</v>
+        <v>4940</v>
       </c>
       <c r="C18" s="2">
-        <v>13.31</v>
+        <v>9.73</v>
       </c>
       <c r="D18" s="2">
-        <v>-7.35</v>
+        <v>-5.53</v>
       </c>
       <c r="E18" s="2">
-        <v>-5.28</v>
+        <v>-5.62</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
+        <v>76</v>
+      </c>
+      <c r="H18" s="2">
         <v>70</v>
-      </c>
-      <c r="H18" s="2">
-        <v>64</v>
       </c>
       <c r="I18" s="2">
         <v>64</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1275.6</v>
+        <v>1755</v>
       </c>
       <c r="C19" s="2">
-        <v>-0.76</v>
+        <v>-7.72</v>
       </c>
       <c r="D19" s="2">
-        <v>3.09</v>
+        <v>-3.81</v>
       </c>
       <c r="E19" s="2">
-        <v>-3.87</v>
+        <v>0.83</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="H19" s="2">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="I19" s="2">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>996.2</v>
+        <v>269.5</v>
       </c>
       <c r="C20" s="2">
-        <v>6.05</v>
+        <v>-8.33</v>
       </c>
       <c r="D20" s="2">
-        <v>-3.93</v>
+        <v>-6.22</v>
       </c>
       <c r="E20" s="2">
-        <v>-4.17</v>
+        <v>2.26</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1338.9</v>
+        <v>3166.5</v>
       </c>
       <c r="C21" s="2">
-        <v>7.92</v>
+        <v>0.15</v>
       </c>
       <c r="D21" s="2">
-        <v>-4.21</v>
+        <v>1.04</v>
       </c>
       <c r="E21" s="2">
-        <v>-5.38</v>
+        <v>-6.07</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H21" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I21" s="2">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>2789</v>
+        <v>996.9</v>
       </c>
       <c r="C22" s="2">
-        <v>3.9</v>
+        <v>6.49</v>
       </c>
       <c r="D22" s="2">
-        <v>-3.83</v>
+        <v>-6.31</v>
       </c>
       <c r="E22" s="2">
-        <v>-3.99</v>
+        <v>-5.69</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="H22" s="2">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="I22" s="2">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1867.3</v>
+        <v>3876.2</v>
       </c>
       <c r="C23" s="2">
-        <v>-1.76</v>
+        <v>-3.9</v>
       </c>
       <c r="D23" s="2">
-        <v>-2.82</v>
+        <v>0.97</v>
       </c>
       <c r="E23" s="2">
-        <v>-2.24</v>
+        <v>-4.17</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H23" s="2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="I23" s="2">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1766.9</v>
+        <v>1014</v>
       </c>
       <c r="C24" s="2">
-        <v>-5.03</v>
+        <v>1.49</v>
       </c>
       <c r="D24" s="2">
-        <v>-4.8</v>
+        <v>-8.02</v>
       </c>
       <c r="E24" s="2">
-        <v>0.29</v>
+        <v>-2.7</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="H24" s="2">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="I24" s="2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1394.5</v>
+        <v>1785.4</v>
       </c>
       <c r="C25" s="2">
-        <v>-1.31</v>
+        <v>-3.57</v>
       </c>
       <c r="D25" s="2">
-        <v>-2.26</v>
+        <v>-6.82</v>
       </c>
       <c r="E25" s="2">
-        <v>-3.02</v>
+        <v>-1.46</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H25" s="2">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I25" s="2">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>3885</v>
+        <v>977</v>
       </c>
       <c r="C26" s="2">
-        <v>0.13</v>
+        <v>-10.69</v>
       </c>
       <c r="D26" s="2">
-        <v>-1.11</v>
+        <v>3.08</v>
       </c>
       <c r="E26" s="2">
-        <v>-5.01</v>
+        <v>-3.79</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="H26" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I26" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>185.54</v>
+        <v>11056</v>
       </c>
       <c r="C27" s="2">
-        <v>-9.699999999999999</v>
+        <v>-3.79</v>
       </c>
       <c r="D27" s="2">
-        <v>-0.84</v>
+        <v>-5.22</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.41</v>
+        <v>-3.44</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I27" s="2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,16 +1554,16 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1852.5</v>
+        <v>7360</v>
       </c>
       <c r="C28" s="2">
-        <v>5.76</v>
+        <v>0.31</v>
       </c>
       <c r="D28" s="2">
-        <v>-2.91</v>
+        <v>-1.67</v>
       </c>
       <c r="E28" s="2">
-        <v>-7.45</v>
+        <v>-7.46</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
@@ -1572,10 +1572,10 @@
         <v>74</v>
       </c>
       <c r="H28" s="2">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="I28" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>550.95</v>
+        <v>235.86</v>
       </c>
       <c r="C29" s="2">
-        <v>-8.6</v>
+        <v>-16.88</v>
       </c>
       <c r="D29" s="2">
-        <v>-3.92</v>
+        <v>-5.1</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.36</v>
+        <v>2.18</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H29" s="2">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I29" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>731</v>
+        <v>1849.9</v>
       </c>
       <c r="C30" s="2">
-        <v>-3.33</v>
+        <v>0.77</v>
       </c>
       <c r="D30" s="2">
-        <v>-10.63</v>
+        <v>-5.44</v>
       </c>
       <c r="E30" s="2">
-        <v>0.27</v>
+        <v>-6.8</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H30" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I30" s="2">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>11014</v>
+        <v>326.6</v>
       </c>
       <c r="C31" s="2">
-        <v>-2.79</v>
+        <v>-15.36</v>
       </c>
       <c r="D31" s="2">
-        <v>-2.87</v>
+        <v>-4.93</v>
       </c>
       <c r="E31" s="2">
-        <v>-4.26</v>
+        <v>0.83</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H31" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I31" s="2">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>1010</v>
+        <v>393.55</v>
       </c>
       <c r="C32" s="2">
-        <v>8.779999999999999</v>
+        <v>-6.58</v>
       </c>
       <c r="D32" s="2">
-        <v>-3.64</v>
+        <v>-3.45</v>
       </c>
       <c r="E32" s="2">
-        <v>-9.74</v>
+        <v>-5.04</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I32" s="2">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>270.3</v>
+        <v>983</v>
       </c>
       <c r="C33" s="2">
-        <v>-8.85</v>
+        <v>1.38</v>
       </c>
       <c r="D33" s="2">
-        <v>-5.49</v>
+        <v>-7.26</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.41</v>
+        <v>-7.26</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H33" s="2">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="I33" s="2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1185</v>
+        <v>1222.4</v>
       </c>
       <c r="C34" s="2">
-        <v>-10.42</v>
+        <v>-6.7</v>
       </c>
       <c r="D34" s="2">
-        <v>-4.01</v>
+        <v>-2.68</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.42</v>
+        <v>-5.97</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H34" s="2">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="I34" s="2">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>229.89</v>
+        <v>3035</v>
       </c>
       <c r="C35" s="2">
-        <v>-0.95</v>
+        <v>-2.3</v>
       </c>
       <c r="D35" s="2">
-        <v>-4.55</v>
+        <v>-4.12</v>
       </c>
       <c r="E35" s="2">
-        <v>-5</v>
+        <v>-7.53</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H35" s="2">
         <v>34</v>
       </c>
       <c r="I35" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>393.3</v>
+        <v>1326.8</v>
       </c>
       <c r="C36" s="2">
-        <v>-7.68</v>
+        <v>3.58</v>
       </c>
       <c r="D36" s="2">
-        <v>-4.13</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="E36" s="2">
-        <v>-3.84</v>
+        <v>-8.75</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H36" s="2">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="I36" s="2">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1372.4</v>
+        <v>1942.9</v>
       </c>
       <c r="C37" s="2">
-        <v>-3.68</v>
+        <v>-10.65</v>
       </c>
       <c r="D37" s="2">
-        <v>-3.83</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E37" s="2">
-        <v>-6.72</v>
+        <v>-1.25</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H37" s="2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I37" s="2">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>972.7</v>
+        <v>990</v>
       </c>
       <c r="C38" s="2">
-        <v>-7.15</v>
+        <v>3.5</v>
       </c>
       <c r="D38" s="2">
-        <v>0.61</v>
+        <v>-4.38</v>
       </c>
       <c r="E38" s="2">
-        <v>-8.109999999999999</v>
+        <v>-10.8</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H38" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I38" s="2">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>1051.4</v>
+        <v>227</v>
       </c>
       <c r="C39" s="2">
-        <v>-5.98</v>
+        <v>-5.88</v>
       </c>
       <c r="D39" s="2">
-        <v>-4.64</v>
+        <v>-4.77</v>
       </c>
       <c r="E39" s="2">
-        <v>-6.96</v>
+        <v>-5.95</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H39" s="2">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I39" s="2">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>3052</v>
+        <v>531</v>
       </c>
       <c r="C40" s="2">
-        <v>0.01</v>
+        <v>-14.05</v>
       </c>
       <c r="D40" s="2">
-        <v>-3.43</v>
+        <v>-5.96</v>
       </c>
       <c r="E40" s="2">
-        <v>-10.61</v>
+        <v>-2.27</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="H40" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I40" s="2">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,25 +1970,25 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>2105</v>
+        <v>1226</v>
       </c>
       <c r="C41" s="2">
-        <v>-6.04</v>
+        <v>-9.9</v>
       </c>
       <c r="D41" s="2">
-        <v>-2.98</v>
+        <v>-7.34</v>
       </c>
       <c r="E41" s="2">
-        <v>-7.84</v>
+        <v>-3.99</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="H41" s="2">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="I41" s="2">
         <v>52</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>262.3</v>
+        <v>1362.6</v>
       </c>
       <c r="C42" s="2">
-        <v>-13.12</v>
+        <v>-3.14</v>
       </c>
       <c r="D42" s="2">
-        <v>-6.2</v>
+        <v>-5.79</v>
       </c>
       <c r="E42" s="2">
-        <v>-2.74</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H42" s="2">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="I42" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1226.4</v>
+        <v>2669.3</v>
       </c>
       <c r="C43" s="2">
-        <v>-7.77</v>
+        <v>-6.75</v>
       </c>
       <c r="D43" s="2">
-        <v>-5.44</v>
+        <v>-8.77</v>
       </c>
       <c r="E43" s="2">
-        <v>-6.37</v>
+        <v>-7.31</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="H43" s="2">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="I43" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>2451.3</v>
+        <v>1771</v>
       </c>
       <c r="C44" s="2">
-        <v>-5.41</v>
+        <v>-1.93</v>
       </c>
       <c r="D44" s="2">
-        <v>-7.57</v>
+        <v>-4.86</v>
       </c>
       <c r="E44" s="2">
-        <v>-7.18</v>
+        <v>-12.37</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="H44" s="2">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="I44" s="2">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>232.8</v>
+        <v>2444</v>
       </c>
       <c r="C45" s="2">
-        <v>-21.34</v>
+        <v>-7.25</v>
       </c>
       <c r="D45" s="2">
-        <v>-5.9</v>
+        <v>-9.19</v>
       </c>
       <c r="E45" s="2">
-        <v>-1.17</v>
+        <v>-7.9</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H45" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I45" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,25 +2130,25 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>323.65</v>
+        <v>983.2</v>
       </c>
       <c r="C46" s="2">
-        <v>-15.75</v>
+        <v>-17.18</v>
       </c>
       <c r="D46" s="2">
-        <v>-6.99</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="E46" s="2">
-        <v>-3.64</v>
+        <v>-5.23</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="H46" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I46" s="2">
         <v>2</v>
@@ -2162,22 +2162,22 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>1942.2</v>
+        <v>12065</v>
       </c>
       <c r="C47" s="2">
-        <v>-12.96</v>
+        <v>-7.47</v>
       </c>
       <c r="D47" s="2">
-        <v>-8.84</v>
+        <v>-9.83</v>
       </c>
       <c r="E47" s="2">
-        <v>-4.33</v>
+        <v>-10.94</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H47" s="2">
         <v>8</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>303.8</v>
+        <v>2082</v>
       </c>
       <c r="C48" s="2">
-        <v>-13.26</v>
+        <v>-9.31</v>
       </c>
       <c r="D48" s="2">
-        <v>-11.23</v>
+        <v>-7.51</v>
       </c>
       <c r="E48" s="2">
-        <v>-3.37</v>
+        <v>-13.22</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H48" s="2">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="I48" s="2">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>166.83</v>
+        <v>1000.2</v>
       </c>
       <c r="C49" s="2">
-        <v>-12.19</v>
+        <v>-12.55</v>
       </c>
       <c r="D49" s="2">
-        <v>-5.43</v>
+        <v>-7.99</v>
       </c>
       <c r="E49" s="2">
-        <v>-7.99</v>
+        <v>-11.78</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H49" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I49" s="2">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>1013.7</v>
+        <v>290.45</v>
       </c>
       <c r="C50" s="2">
-        <v>-16.96</v>
+        <v>-21.54</v>
       </c>
       <c r="D50" s="2">
-        <v>-7.73</v>
+        <v>-13.67</v>
       </c>
       <c r="E50" s="2">
-        <v>-4.59</v>
+        <v>-5.96</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H50" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I50" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>12103</v>
+        <v>164.02</v>
       </c>
       <c r="C51" s="2">
-        <v>-6.08</v>
+        <v>-19.8</v>
       </c>
       <c r="D51" s="2">
-        <v>-10.74</v>
+        <v>-5.95</v>
       </c>
       <c r="E51" s="2">
-        <v>-11.14</v>
+        <v>-11.1</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H51" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I51" s="2">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>326.85</v>
+        <v>335</v>
       </c>
       <c r="C2" s="2">
-        <v>35.4</v>
+        <v>35.26</v>
       </c>
       <c r="D2" s="2">
-        <v>14.6</v>
+        <v>16.75</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.09</v>
+        <v>2.1</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2488,51 +2488,51 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>416.5</v>
+        <v>4884</v>
       </c>
       <c r="C3" s="2">
-        <v>6.49</v>
+        <v>17.81</v>
       </c>
       <c r="D3" s="2">
-        <v>8.470000000000001</v>
+        <v>5.18</v>
       </c>
       <c r="E3" s="2">
-        <v>3.75</v>
+        <v>-4.28</v>
       </c>
       <c r="F3" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H3" s="2">
         <v>96</v>
       </c>
       <c r="I3" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1">
-        <v>11414</v>
+        <v>405</v>
       </c>
       <c r="C4" s="2">
-        <v>13.49</v>
+        <v>3.27</v>
       </c>
       <c r="D4" s="2">
-        <v>9.949999999999999</v>
+        <v>6.01</v>
       </c>
       <c r="E4" s="2">
-        <v>-3.27</v>
+        <v>-3.43</v>
       </c>
       <c r="F4" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G4" s="2">
         <v>94</v>
@@ -2546,93 +2546,64 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
-        <v>4798.5</v>
+        <v>11208</v>
       </c>
       <c r="C5" s="2">
-        <v>15.46</v>
+        <v>8.34</v>
       </c>
       <c r="D5" s="2">
-        <v>4.28</v>
+        <v>6.51</v>
       </c>
       <c r="E5" s="2">
-        <v>-5.52</v>
+        <v>-7.6</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G5" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2">
         <v>94</v>
       </c>
       <c r="I5" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
-        <v>1537.1</v>
+        <v>1548</v>
       </c>
       <c r="C6" s="2">
-        <v>10.28</v>
+        <v>10.64</v>
       </c>
       <c r="D6" s="2">
-        <v>2.17</v>
+        <v>-1.8</v>
       </c>
       <c r="E6" s="2">
-        <v>-2.96</v>
+        <v>-4.91</v>
       </c>
       <c r="F6" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G6" s="2">
+        <v>82</v>
+      </c>
+      <c r="H6" s="2">
         <v>88</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>90</v>
       </c>
-      <c r="I6" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3187</v>
-      </c>
-      <c r="C7" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1.67</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-3.07</v>
-      </c>
-      <c r="F7" s="2">
-        <v>82</v>
-      </c>
-      <c r="G7" s="2">
-        <v>90</v>
-      </c>
-      <c r="H7" s="2">
-        <v>92</v>
-      </c>
-      <c r="I7" s="2">
-        <v>88</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2640,7 +2611,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2648,7 +2619,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2656,22 +2627,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2682,7 +2653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2724,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>326.85</v>
+        <v>335</v>
       </c>
       <c r="C2" s="2">
-        <v>35.4</v>
+        <v>35.26</v>
       </c>
       <c r="D2" s="2">
-        <v>14.6</v>
+        <v>16.75</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.09</v>
+        <v>2.1</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2753,16 +2724,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>416.5</v>
+        <v>1785.3</v>
       </c>
       <c r="C3" s="2">
-        <v>6.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D3" s="2">
-        <v>8.470000000000001</v>
+        <v>-3.18</v>
       </c>
       <c r="E3" s="2">
-        <v>3.75</v>
+        <v>12.06</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2771,10 +2742,10 @@
         <v>98</v>
       </c>
       <c r="H3" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I3" s="2">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2782,177 +2753,148 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1824</v>
+        <v>4884</v>
       </c>
       <c r="C4" s="2">
-        <v>2.46</v>
+        <v>17.81</v>
       </c>
       <c r="D4" s="2">
-        <v>0.76</v>
+        <v>5.18</v>
       </c>
       <c r="E4" s="2">
-        <v>9.08</v>
+        <v>-4.28</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2">
-        <v>56</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>11414</v>
+        <v>8889</v>
       </c>
       <c r="C5" s="2">
-        <v>13.49</v>
+        <v>5.89</v>
       </c>
       <c r="D5" s="2">
-        <v>9.949999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="E5" s="2">
-        <v>-3.27</v>
+        <v>-0.11</v>
       </c>
       <c r="F5" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>8768.5</v>
+        <v>405</v>
       </c>
       <c r="C6" s="2">
-        <v>9.449999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="D6" s="2">
-        <v>-0.04</v>
+        <v>6.01</v>
       </c>
       <c r="E6" s="2">
-        <v>0.76</v>
+        <v>-3.43</v>
       </c>
       <c r="F6" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G6" s="2">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="I6" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>4798.5</v>
+        <v>11208</v>
       </c>
       <c r="C7" s="2">
-        <v>15.46</v>
+        <v>8.34</v>
       </c>
       <c r="D7" s="2">
-        <v>4.28</v>
+        <v>6.51</v>
       </c>
       <c r="E7" s="2">
-        <v>-5.52</v>
+        <v>-7.6</v>
       </c>
       <c r="F7" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G7" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2">
         <v>94</v>
       </c>
       <c r="I7" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>1537.1</v>
+        <v>1548</v>
       </c>
       <c r="C8" s="2">
-        <v>10.28</v>
+        <v>10.64</v>
       </c>
       <c r="D8" s="2">
-        <v>2.17</v>
+        <v>-1.8</v>
       </c>
       <c r="E8" s="2">
-        <v>-2.96</v>
+        <v>-4.91</v>
       </c>
       <c r="F8" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G8" s="2">
+        <v>82</v>
+      </c>
+      <c r="H8" s="2">
         <v>88</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>90</v>
       </c>
-      <c r="I8" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3187</v>
-      </c>
-      <c r="C9" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1.67</v>
-      </c>
-      <c r="E9" s="2">
-        <v>-3.07</v>
-      </c>
-      <c r="F9" s="2">
-        <v>82</v>
-      </c>
-      <c r="G9" s="2">
-        <v>90</v>
-      </c>
-      <c r="H9" s="2">
-        <v>92</v>
-      </c>
-      <c r="I9" s="2">
-        <v>88</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2960,7 +2902,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2968,7 +2910,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2976,22 +2918,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -3027,7 +2969,7 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2">
         <v>16</v>
@@ -3041,13 +2983,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3055,13 +2997,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3069,13 +3011,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-09-25</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-09-25</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-09-25</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-09-25</t>
+    <t>Price_2026-10-02</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-10-02</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-10-02</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-10-02</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-10-02</t>
   </si>
   <si>
     <t>RS_Score_2026-09-25</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-09-11</t>
   </si>
   <si>
-    <t>RS_Score_2026-09-04</t>
-  </si>
-  <si>
     <t>ETERNAL</t>
   </si>
   <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
     <t>ADANIPORTS</t>
   </si>
   <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
     <t>TITAN</t>
   </si>
   <si>
-    <t>COALINDIA</t>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>ADANIENT</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
   </si>
   <si>
     <t>APOLLOHOSP</t>
   </si>
   <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
   </si>
   <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>ADANIENT</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
     <t>MARUTI</t>
   </si>
   <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>INFY</t>
+    <t>WIPRO</t>
   </si>
   <si>
     <t>TMPV</t>
   </si>
   <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
     <t>2026-09-25</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>335</v>
+        <v>313.9</v>
       </c>
       <c r="C2" s="2">
-        <v>35.26</v>
+        <v>25.27</v>
       </c>
       <c r="D2" s="2">
-        <v>16.75</v>
+        <v>12.11</v>
       </c>
       <c r="E2" s="2">
-        <v>2.1</v>
+        <v>-2.74</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1785.3</v>
+        <v>418.35</v>
       </c>
       <c r="C3" s="2">
-        <v>-0.5600000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="D3" s="2">
-        <v>-3.18</v>
+        <v>8.73</v>
       </c>
       <c r="E3" s="2">
-        <v>12.06</v>
+        <v>-1.45</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>86</v>
+      </c>
+      <c r="H3" s="2">
+        <v>94</v>
+      </c>
+      <c r="I3" s="2">
         <v>98</v>
-      </c>
-      <c r="H3" s="2">
-        <v>82</v>
-      </c>
-      <c r="I3" s="2">
-        <v>66</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>4884</v>
+        <v>4929.9</v>
       </c>
       <c r="C4" s="2">
-        <v>17.81</v>
+        <v>11.92</v>
       </c>
       <c r="D4" s="2">
-        <v>5.18</v>
+        <v>-1.11</v>
       </c>
       <c r="E4" s="2">
-        <v>-4.28</v>
+        <v>-0.95</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H4" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>426.1</v>
+        <v>1206.2</v>
       </c>
       <c r="C5" s="2">
-        <v>-4.53</v>
+        <v>-6.88</v>
       </c>
       <c r="D5" s="2">
-        <v>1.83</v>
+        <v>4.73</v>
       </c>
       <c r="E5" s="2">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="I5" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>8889</v>
+        <v>1737.8</v>
       </c>
       <c r="C6" s="2">
-        <v>5.89</v>
+        <v>-3.3</v>
       </c>
       <c r="D6" s="2">
-        <v>-0.06</v>
+        <v>-1.72</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.11</v>
+        <v>1.79</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H6" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I6" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1258</v>
+        <v>721.2</v>
       </c>
       <c r="C7" s="2">
-        <v>9.02</v>
+        <v>-1.53</v>
       </c>
       <c r="D7" s="2">
-        <v>3</v>
+        <v>-2.91</v>
       </c>
       <c r="E7" s="2">
-        <v>-4.13</v>
+        <v>1.28</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H7" s="2">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="I7" s="2">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,16 +914,16 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>405</v>
+        <v>420.4</v>
       </c>
       <c r="C8" s="2">
-        <v>3.27</v>
+        <v>-5.79</v>
       </c>
       <c r="D8" s="2">
-        <v>6.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E8" s="2">
-        <v>-3.43</v>
+        <v>1.22</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
@@ -932,10 +932,10 @@
         <v>94</v>
       </c>
       <c r="H8" s="2">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="I8" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>11208</v>
+        <v>1533</v>
       </c>
       <c r="C9" s="2">
-        <v>8.34</v>
+        <v>5.99</v>
       </c>
       <c r="D9" s="2">
-        <v>6.51</v>
+        <v>-1.7</v>
       </c>
       <c r="E9" s="2">
-        <v>-7.6</v>
+        <v>-4</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H9" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I9" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1548</v>
+        <v>1243.1</v>
       </c>
       <c r="C10" s="2">
-        <v>10.64</v>
+        <v>6.08</v>
       </c>
       <c r="D10" s="2">
-        <v>-1.8</v>
+        <v>-2.2</v>
       </c>
       <c r="E10" s="2">
-        <v>-4.91</v>
+        <v>-3.89</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H10" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="I10" s="2">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>735.6</v>
+        <v>4515.7</v>
       </c>
       <c r="C11" s="2">
-        <v>-4.97</v>
+        <v>11.18</v>
       </c>
       <c r="D11" s="2">
-        <v>-5.4</v>
+        <v>-3.45</v>
       </c>
       <c r="E11" s="2">
-        <v>3.75</v>
+        <v>-10.05</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H11" s="2">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I11" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1201</v>
+        <v>1344</v>
       </c>
       <c r="C12" s="2">
-        <v>-9.220000000000001</v>
+        <v>-3.17</v>
       </c>
       <c r="D12" s="2">
-        <v>-1.81</v>
+        <v>-4.72</v>
       </c>
       <c r="E12" s="2">
-        <v>4.04</v>
+        <v>-2.96</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I12" s="2">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>269</v>
+        <v>1217.1</v>
       </c>
       <c r="C13" s="2">
-        <v>-9.09</v>
+        <v>-5.33</v>
       </c>
       <c r="D13" s="2">
-        <v>-4.85</v>
+        <v>-0.83</v>
       </c>
       <c r="E13" s="2">
-        <v>5.28</v>
+        <v>-4.39</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H13" s="2">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="I13" s="2">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1277</v>
+        <v>1801</v>
       </c>
       <c r="C14" s="2">
-        <v>-0.39</v>
+        <v>0.36</v>
       </c>
       <c r="D14" s="2">
-        <v>1.59</v>
+        <v>-7.22</v>
       </c>
       <c r="E14" s="2">
-        <v>-2.35</v>
+        <v>-5.16</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="H14" s="2">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="I14" s="2">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>187.97</v>
+        <v>1233</v>
       </c>
       <c r="C15" s="2">
-        <v>-8.74</v>
+        <v>-2.97</v>
       </c>
       <c r="D15" s="2">
-        <v>0.84</v>
+        <v>-0.63</v>
       </c>
       <c r="E15" s="2">
-        <v>1.96</v>
+        <v>-6.94</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="H15" s="2">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="I15" s="2">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>2900</v>
+        <v>534.2</v>
       </c>
       <c r="C16" s="2">
-        <v>1.81</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="D16" s="2">
-        <v>-8.9</v>
+        <v>-3.76</v>
       </c>
       <c r="E16" s="2">
-        <v>1.43</v>
+        <v>-2.23</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="H16" s="2">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="I16" s="2">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1399.7</v>
+        <v>1310.6</v>
       </c>
       <c r="C17" s="2">
-        <v>-0.08</v>
+        <v>5.19</v>
       </c>
       <c r="D17" s="2">
-        <v>-2.91</v>
+        <v>-7.76</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.67</v>
+        <v>-7.91</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I17" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>4940</v>
+        <v>2816.8</v>
       </c>
       <c r="C18" s="2">
-        <v>9.73</v>
+        <v>-4.06</v>
       </c>
       <c r="D18" s="2">
-        <v>-5.53</v>
+        <v>-6.93</v>
       </c>
       <c r="E18" s="2">
-        <v>-5.62</v>
+        <v>-4.13</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I18" s="2">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1755</v>
+        <v>954.1</v>
       </c>
       <c r="C19" s="2">
-        <v>-7.72</v>
+        <v>-1.07</v>
       </c>
       <c r="D19" s="2">
-        <v>-3.81</v>
+        <v>-6</v>
       </c>
       <c r="E19" s="2">
-        <v>0.83</v>
+        <v>-6.1</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H19" s="2">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="I19" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>269.5</v>
+        <v>1721.6</v>
       </c>
       <c r="C20" s="2">
-        <v>-8.33</v>
+        <v>-5.93</v>
       </c>
       <c r="D20" s="2">
-        <v>-6.22</v>
+        <v>-7.37</v>
       </c>
       <c r="E20" s="2">
-        <v>2.26</v>
+        <v>-3.01</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I20" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>3166.5</v>
+        <v>8133.5</v>
       </c>
       <c r="C21" s="2">
-        <v>0.15</v>
+        <v>-0.41</v>
       </c>
       <c r="D21" s="2">
-        <v>1.04</v>
+        <v>-7.52</v>
       </c>
       <c r="E21" s="2">
-        <v>-6.07</v>
+        <v>-5.97</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H21" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I21" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>996.9</v>
+        <v>948.3</v>
       </c>
       <c r="C22" s="2">
-        <v>6.49</v>
+        <v>5.05</v>
       </c>
       <c r="D22" s="2">
-        <v>-6.31</v>
+        <v>-6.37</v>
       </c>
       <c r="E22" s="2">
-        <v>-5.69</v>
+        <v>-10.58</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
+        <v>62</v>
+      </c>
+      <c r="H22" s="2">
         <v>86</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <v>78</v>
-      </c>
-      <c r="I22" s="2">
-        <v>80</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>3876.2</v>
+        <v>1741.1</v>
       </c>
       <c r="C23" s="2">
-        <v>-3.9</v>
+        <v>-3.61</v>
       </c>
       <c r="D23" s="2">
-        <v>0.97</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="E23" s="2">
-        <v>-4.17</v>
+        <v>-5.38</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H23" s="2">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I23" s="2">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1014</v>
+        <v>383.1</v>
       </c>
       <c r="C24" s="2">
-        <v>1.49</v>
+        <v>-6.6</v>
       </c>
       <c r="D24" s="2">
-        <v>-8.02</v>
+        <v>-5.28</v>
       </c>
       <c r="E24" s="2">
-        <v>-2.7</v>
+        <v>-5.49</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="I24" s="2">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1785.4</v>
+        <v>945</v>
       </c>
       <c r="C25" s="2">
-        <v>-3.57</v>
+        <v>0.34</v>
       </c>
       <c r="D25" s="2">
-        <v>-6.82</v>
+        <v>-5.98</v>
       </c>
       <c r="E25" s="2">
-        <v>-1.46</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="H25" s="2">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I25" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>977</v>
+        <v>940.95</v>
       </c>
       <c r="C26" s="2">
-        <v>-10.69</v>
+        <v>-2.33</v>
       </c>
       <c r="D26" s="2">
-        <v>3.08</v>
+        <v>-12.91</v>
       </c>
       <c r="E26" s="2">
-        <v>-3.79</v>
+        <v>-4.45</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H26" s="2">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="I26" s="2">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>11056</v>
+        <v>10710</v>
       </c>
       <c r="C27" s="2">
-        <v>-3.79</v>
+        <v>-4.82</v>
       </c>
       <c r="D27" s="2">
-        <v>-5.22</v>
+        <v>-7.74</v>
       </c>
       <c r="E27" s="2">
-        <v>-3.44</v>
+        <v>-6.12</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
+        <v>56</v>
+      </c>
+      <c r="H27" s="2">
         <v>46</v>
       </c>
-      <c r="H27" s="2">
+      <c r="I27" s="2">
         <v>38</v>
-      </c>
-      <c r="I27" s="2">
-        <v>50</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>7360</v>
+        <v>3693.4</v>
       </c>
       <c r="C28" s="2">
-        <v>0.31</v>
+        <v>-9.4</v>
       </c>
       <c r="D28" s="2">
-        <v>-1.67</v>
+        <v>-2.44</v>
       </c>
       <c r="E28" s="2">
-        <v>-7.46</v>
+        <v>-6.83</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="H28" s="2">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="I28" s="2">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>235.86</v>
+        <v>1035</v>
       </c>
       <c r="C29" s="2">
-        <v>-16.88</v>
+        <v>-8.92</v>
       </c>
       <c r="D29" s="2">
-        <v>-5.1</v>
+        <v>-0.57</v>
       </c>
       <c r="E29" s="2">
-        <v>2.18</v>
+        <v>-8.41</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H29" s="2">
         <v>26</v>
       </c>
       <c r="I29" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>1849.9</v>
+        <v>178</v>
       </c>
       <c r="C30" s="2">
-        <v>0.77</v>
+        <v>-12.67</v>
       </c>
       <c r="D30" s="2">
-        <v>-5.44</v>
+        <v>-2.56</v>
       </c>
       <c r="E30" s="2">
-        <v>-6.8</v>
+        <v>-5.72</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="H30" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I30" s="2">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>326.6</v>
+        <v>255.9</v>
       </c>
       <c r="C31" s="2">
-        <v>-15.36</v>
+        <v>-10.81</v>
       </c>
       <c r="D31" s="2">
-        <v>-4.93</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="E31" s="2">
-        <v>0.83</v>
+        <v>-3.1</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
+        <v>76</v>
+      </c>
+      <c r="H31" s="2">
+        <v>20</v>
+      </c>
+      <c r="I31" s="2">
         <v>12</v>
-      </c>
-      <c r="H31" s="2">
-        <v>40</v>
-      </c>
-      <c r="I31" s="2">
-        <v>18</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>393.55</v>
+        <v>2407</v>
       </c>
       <c r="C32" s="2">
-        <v>-6.58</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="D32" s="2">
-        <v>-3.45</v>
+        <v>-8.75</v>
       </c>
       <c r="E32" s="2">
-        <v>-5.04</v>
+        <v>-4.76</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H32" s="2">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I32" s="2">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>983</v>
+        <v>6920</v>
       </c>
       <c r="C33" s="2">
-        <v>1.38</v>
+        <v>-2.57</v>
       </c>
       <c r="D33" s="2">
-        <v>-7.26</v>
+        <v>-8.33</v>
       </c>
       <c r="E33" s="2">
-        <v>-7.26</v>
+        <v>-9.31</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="H33" s="2">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="I33" s="2">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1222.4</v>
+        <v>941.85</v>
       </c>
       <c r="C34" s="2">
-        <v>-6.7</v>
+        <v>-15.97</v>
       </c>
       <c r="D34" s="2">
-        <v>-2.68</v>
+        <v>-0.1</v>
       </c>
       <c r="E34" s="2">
-        <v>-5.97</v>
+        <v>-6.84</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="I34" s="2">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>3035</v>
+        <v>2962</v>
       </c>
       <c r="C35" s="2">
-        <v>-2.3</v>
+        <v>-4.84</v>
       </c>
       <c r="D35" s="2">
-        <v>-4.12</v>
+        <v>-3.83</v>
       </c>
       <c r="E35" s="2">
-        <v>-7.53</v>
+        <v>-10.84</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="H35" s="2">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="I35" s="2">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1326.8</v>
+        <v>1307.7</v>
       </c>
       <c r="C36" s="2">
-        <v>3.58</v>
+        <v>-7.56</v>
       </c>
       <c r="D36" s="2">
-        <v>-8.369999999999999</v>
+        <v>-9.41</v>
       </c>
       <c r="E36" s="2">
-        <v>-8.75</v>
+        <v>-7.29</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="I36" s="2">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1942.9</v>
+        <v>254.55</v>
       </c>
       <c r="C37" s="2">
-        <v>-10.65</v>
+        <v>-11.98</v>
       </c>
       <c r="D37" s="2">
-        <v>-9.199999999999999</v>
+        <v>-11.26</v>
       </c>
       <c r="E37" s="2">
-        <v>-1.25</v>
+        <v>-4.3</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="H37" s="2">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="I37" s="2">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>990</v>
+        <v>2860</v>
       </c>
       <c r="C38" s="2">
-        <v>3.5</v>
+        <v>-5.11</v>
       </c>
       <c r="D38" s="2">
-        <v>-4.38</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="E38" s="2">
-        <v>-10.8</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H38" s="2">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="I38" s="2">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>227</v>
+        <v>1732.6</v>
       </c>
       <c r="C39" s="2">
-        <v>-5.88</v>
+        <v>-2.78</v>
       </c>
       <c r="D39" s="2">
-        <v>-4.77</v>
+        <v>-7.68</v>
       </c>
       <c r="E39" s="2">
-        <v>-5.95</v>
+        <v>-12.05</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="H39" s="2">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="I39" s="2">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>531</v>
+        <v>2075</v>
       </c>
       <c r="C40" s="2">
-        <v>-14.05</v>
+        <v>-7.64</v>
       </c>
       <c r="D40" s="2">
-        <v>-5.96</v>
+        <v>-7.95</v>
       </c>
       <c r="E40" s="2">
-        <v>-2.27</v>
+        <v>-9.94</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="H40" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I40" s="2">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1226</v>
+        <v>315.1</v>
       </c>
       <c r="C41" s="2">
-        <v>-9.9</v>
+        <v>-17.68</v>
       </c>
       <c r="D41" s="2">
-        <v>-7.34</v>
+        <v>-8.27</v>
       </c>
       <c r="E41" s="2">
-        <v>-3.99</v>
+        <v>-5.23</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H41" s="2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I41" s="2">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>1362.6</v>
+        <v>222.37</v>
       </c>
       <c r="C42" s="2">
-        <v>-3.14</v>
+        <v>-15.86</v>
       </c>
       <c r="D42" s="2">
-        <v>-5.79</v>
+        <v>-10.23</v>
       </c>
       <c r="E42" s="2">
-        <v>-8.949999999999999</v>
+        <v>-5.23</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I42" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>2669.3</v>
+        <v>2580</v>
       </c>
       <c r="C43" s="2">
-        <v>-6.75</v>
+        <v>-8.25</v>
       </c>
       <c r="D43" s="2">
-        <v>-8.77</v>
+        <v>-10.74</v>
       </c>
       <c r="E43" s="2">
-        <v>-7.31</v>
+        <v>-9.57</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
+        <v>18</v>
+      </c>
+      <c r="H43" s="2">
         <v>70</v>
       </c>
-      <c r="H43" s="2">
+      <c r="I43" s="2">
         <v>28</v>
-      </c>
-      <c r="I43" s="2">
-        <v>24</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1771</v>
+        <v>957</v>
       </c>
       <c r="C44" s="2">
-        <v>-1.93</v>
+        <v>-18.79</v>
       </c>
       <c r="D44" s="2">
-        <v>-4.86</v>
+        <v>-12.04</v>
       </c>
       <c r="E44" s="2">
-        <v>-12.37</v>
+        <v>-5.25</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="H44" s="2">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="I44" s="2">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>2444</v>
+        <v>1836</v>
       </c>
       <c r="C45" s="2">
-        <v>-7.25</v>
+        <v>-13.88</v>
       </c>
       <c r="D45" s="2">
-        <v>-9.19</v>
+        <v>-14.41</v>
       </c>
       <c r="E45" s="2">
-        <v>-7.9</v>
+        <v>-6.96</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H45" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I45" s="2">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>983.2</v>
+        <v>212.5</v>
       </c>
       <c r="C46" s="2">
-        <v>-17.18</v>
+        <v>-10.86</v>
       </c>
       <c r="D46" s="2">
-        <v>-9.960000000000001</v>
+        <v>-9.25</v>
       </c>
       <c r="E46" s="2">
-        <v>-5.23</v>
+        <v>-11.27</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H46" s="2">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="I46" s="2">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>12065</v>
+        <v>1167.7</v>
       </c>
       <c r="C47" s="2">
-        <v>-7.47</v>
+        <v>-11.21</v>
       </c>
       <c r="D47" s="2">
-        <v>-9.83</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="E47" s="2">
-        <v>-10.94</v>
+        <v>-11.67</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H47" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I47" s="2">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>2082</v>
+        <v>10045</v>
       </c>
       <c r="C48" s="2">
-        <v>-9.31</v>
+        <v>-3.97</v>
       </c>
       <c r="D48" s="2">
-        <v>-7.51</v>
+        <v>-9.75</v>
       </c>
       <c r="E48" s="2">
-        <v>-13.22</v>
+        <v>-15.72</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="H48" s="2">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="I48" s="2">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>1000.2</v>
+        <v>11386</v>
       </c>
       <c r="C49" s="2">
-        <v>-12.55</v>
+        <v>-12.39</v>
       </c>
       <c r="D49" s="2">
-        <v>-7.99</v>
+        <v>-14.44</v>
       </c>
       <c r="E49" s="2">
-        <v>-11.78</v>
+        <v>-10.3</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H49" s="2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I49" s="2">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>290.45</v>
+        <v>159.35</v>
       </c>
       <c r="C50" s="2">
-        <v>-21.54</v>
+        <v>-21.09</v>
       </c>
       <c r="D50" s="2">
-        <v>-13.67</v>
+        <v>-9.01</v>
       </c>
       <c r="E50" s="2">
-        <v>-5.96</v>
+        <v>-9.67</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
+        <v>2</v>
+      </c>
+      <c r="H50" s="2">
+        <v>6</v>
+      </c>
+      <c r="I50" s="2">
         <v>10</v>
-      </c>
-      <c r="H50" s="2">
-        <v>4</v>
-      </c>
-      <c r="I50" s="2">
-        <v>4</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>164.02</v>
+        <v>279.4</v>
       </c>
       <c r="C51" s="2">
-        <v>-19.8</v>
+        <v>-28.48</v>
       </c>
       <c r="D51" s="2">
-        <v>-5.95</v>
+        <v>-13.71</v>
       </c>
       <c r="E51" s="2">
-        <v>-11.1</v>
+        <v>-10.3</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H51" s="2">
         <v>10</v>
       </c>
       <c r="I51" s="2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>335</v>
+        <v>313.9</v>
       </c>
       <c r="C2" s="2">
-        <v>35.26</v>
+        <v>25.27</v>
       </c>
       <c r="D2" s="2">
-        <v>16.75</v>
+        <v>12.11</v>
       </c>
       <c r="E2" s="2">
-        <v>2.1</v>
+        <v>-2.74</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2488,60 +2488,60 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>4884</v>
+        <v>418.35</v>
       </c>
       <c r="C3" s="2">
-        <v>17.81</v>
+        <v>9.08</v>
       </c>
       <c r="D3" s="2">
-        <v>5.18</v>
+        <v>8.73</v>
       </c>
       <c r="E3" s="2">
-        <v>-4.28</v>
+        <v>-1.45</v>
       </c>
       <c r="F3" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I3" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>405</v>
+        <v>1737.8</v>
       </c>
       <c r="C4" s="2">
-        <v>3.27</v>
+        <v>-3.3</v>
       </c>
       <c r="D4" s="2">
-        <v>6.01</v>
+        <v>-1.72</v>
       </c>
       <c r="E4" s="2">
-        <v>-3.43</v>
+        <v>1.79</v>
       </c>
       <c r="F4" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
         <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2549,57 +2549,57 @@
         <v>16</v>
       </c>
       <c r="B5" s="1">
-        <v>11208</v>
+        <v>1533</v>
       </c>
       <c r="C5" s="2">
-        <v>8.34</v>
+        <v>5.99</v>
       </c>
       <c r="D5" s="2">
-        <v>6.51</v>
+        <v>-1.7</v>
       </c>
       <c r="E5" s="2">
-        <v>-7.6</v>
+        <v>-4</v>
       </c>
       <c r="F5" s="2">
         <v>86</v>
       </c>
       <c r="G5" s="2">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I5" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1">
-        <v>1548</v>
+        <v>4515.7</v>
       </c>
       <c r="C6" s="2">
-        <v>10.64</v>
+        <v>11.18</v>
       </c>
       <c r="D6" s="2">
-        <v>-1.8</v>
+        <v>-3.45</v>
       </c>
       <c r="E6" s="2">
-        <v>-4.91</v>
+        <v>-10.05</v>
       </c>
       <c r="F6" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G6" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2">
         <v>88</v>
       </c>
       <c r="I6" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2653,7 +2653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>335</v>
+        <v>313.9</v>
       </c>
       <c r="C2" s="2">
-        <v>35.26</v>
+        <v>25.27</v>
       </c>
       <c r="D2" s="2">
-        <v>16.75</v>
+        <v>12.11</v>
       </c>
       <c r="E2" s="2">
-        <v>2.1</v>
+        <v>-2.74</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2724,86 +2724,86 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1785.3</v>
+        <v>418.35</v>
       </c>
       <c r="C3" s="2">
-        <v>-0.5600000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="D3" s="2">
-        <v>-3.18</v>
+        <v>8.73</v>
       </c>
       <c r="E3" s="2">
-        <v>12.06</v>
+        <v>-1.45</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>86</v>
+      </c>
+      <c r="H3" s="2">
+        <v>94</v>
+      </c>
+      <c r="I3" s="2">
         <v>98</v>
-      </c>
-      <c r="H3" s="2">
-        <v>82</v>
-      </c>
-      <c r="I3" s="2">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>4884</v>
+        <v>1737.8</v>
       </c>
       <c r="C4" s="2">
-        <v>17.81</v>
+        <v>-3.3</v>
       </c>
       <c r="D4" s="2">
-        <v>5.18</v>
+        <v>-1.72</v>
       </c>
       <c r="E4" s="2">
-        <v>-4.28</v>
+        <v>1.79</v>
       </c>
       <c r="F4" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>8889</v>
+        <v>721.2</v>
       </c>
       <c r="C5" s="2">
-        <v>5.89</v>
+        <v>-1.53</v>
       </c>
       <c r="D5" s="2">
-        <v>-0.06</v>
+        <v>-2.91</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.11</v>
+        <v>1.28</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="H5" s="2">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="I5" s="2">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2811,16 +2811,16 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>405</v>
+        <v>420.4</v>
       </c>
       <c r="C6" s="2">
-        <v>3.27</v>
+        <v>-5.79</v>
       </c>
       <c r="D6" s="2">
-        <v>6.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E6" s="2">
-        <v>-3.43</v>
+        <v>1.22</v>
       </c>
       <c r="F6" s="2">
         <v>88</v>
@@ -2829,10 +2829,10 @@
         <v>94</v>
       </c>
       <c r="H6" s="2">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="I6" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2840,28 +2840,28 @@
         <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>11208</v>
+        <v>1533</v>
       </c>
       <c r="C7" s="2">
-        <v>8.34</v>
+        <v>5.99</v>
       </c>
       <c r="D7" s="2">
-        <v>6.51</v>
+        <v>-1.7</v>
       </c>
       <c r="E7" s="2">
-        <v>-7.6</v>
+        <v>-4</v>
       </c>
       <c r="F7" s="2">
         <v>86</v>
       </c>
       <c r="G7" s="2">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I7" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2869,32 +2869,61 @@
         <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>1548</v>
+        <v>1243.1</v>
       </c>
       <c r="C8" s="2">
-        <v>10.64</v>
+        <v>6.08</v>
       </c>
       <c r="D8" s="2">
-        <v>-1.8</v>
+        <v>-2.2</v>
       </c>
       <c r="E8" s="2">
-        <v>-4.91</v>
+        <v>-3.89</v>
       </c>
       <c r="F8" s="2">
         <v>84</v>
       </c>
       <c r="G8" s="2">
+        <v>90</v>
+      </c>
+      <c r="H8" s="2">
+        <v>78</v>
+      </c>
+      <c r="I8" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4515.7</v>
+      </c>
+      <c r="C9" s="2">
+        <v>11.18</v>
+      </c>
+      <c r="D9" s="2">
+        <v>-3.45</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-10.05</v>
+      </c>
+      <c r="F9" s="2">
         <v>82</v>
       </c>
-      <c r="H8" s="2">
+      <c r="G9" s="2">
+        <v>96</v>
+      </c>
+      <c r="H9" s="2">
         <v>88</v>
       </c>
-      <c r="I8" s="2">
-        <v>90</v>
+      <c r="I9" s="2">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2902,7 +2931,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2910,7 +2939,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2918,22 +2947,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2969,13 +2998,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2">
         <v>16</v>
-      </c>
-      <c r="D2" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2989,7 +3018,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2997,13 +3026,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3011,13 +3040,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -22,16 +22,19 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-10-02</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-10-02</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-10-02</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-10-02</t>
+    <t>Price_2026-10-09</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-10-09</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-10-09</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-10-09</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-10-09</t>
   </si>
   <si>
     <t>RS_Score_2026-10-02</t>
@@ -43,34 +46,76 @@
     <t>RS_Score_2026-09-18</t>
   </si>
   <si>
-    <t>RS_Score_2026-09-11</t>
+    <t>KOTAKBANK</t>
   </si>
   <si>
     <t>ETERNAL</t>
   </si>
   <si>
-    <t>KOTAKBANK</t>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
   </si>
   <si>
     <t>INDIGO</t>
   </si>
   <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>ITC</t>
   </si>
   <si>
     <t>HDFCBANK</t>
   </si>
   <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
     <t>COALINDIA</t>
   </si>
   <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>LT</t>
   </si>
   <si>
     <t>TITAN</t>
@@ -79,123 +124,78 @@
     <t>CIPLA</t>
   </si>
   <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
   </si>
   <si>
     <t>JSWSTEEL</t>
   </si>
   <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
   </si>
   <si>
     <t>ADANIENT</t>
   </si>
   <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>TMPV</t>
   </si>
   <si>
     <t>MAXHEALTH</t>
   </si>
   <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
     <t>2026-10-02</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>313.9</v>
+        <v>441</v>
       </c>
       <c r="C2" s="2">
-        <v>25.27</v>
+        <v>15.95</v>
       </c>
       <c r="D2" s="2">
-        <v>12.11</v>
+        <v>13.25</v>
       </c>
       <c r="E2" s="2">
-        <v>-2.74</v>
+        <v>5.87</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="I2" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>418.35</v>
+        <v>323.45</v>
       </c>
       <c r="C3" s="2">
-        <v>9.08</v>
+        <v>30.95</v>
       </c>
       <c r="D3" s="2">
-        <v>8.73</v>
+        <v>4.12</v>
       </c>
       <c r="E3" s="2">
-        <v>-1.45</v>
+        <v>0.42</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>4929.9</v>
+        <v>556.65</v>
       </c>
       <c r="C4" s="2">
-        <v>11.92</v>
+        <v>-2.74</v>
       </c>
       <c r="D4" s="2">
-        <v>-1.11</v>
+        <v>2.06</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.95</v>
+        <v>5.8</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H4" s="2">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1206.2</v>
+        <v>1197</v>
       </c>
       <c r="C5" s="2">
-        <v>-6.88</v>
+        <v>-4.65</v>
       </c>
       <c r="D5" s="2">
-        <v>4.73</v>
+        <v>4.56</v>
       </c>
       <c r="E5" s="2">
-        <v>4.8</v>
+        <v>4.72</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="I5" s="2">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1737.8</v>
+        <v>2918.2</v>
       </c>
       <c r="C6" s="2">
-        <v>-3.3</v>
+        <v>2.96</v>
       </c>
       <c r="D6" s="2">
-        <v>-1.72</v>
+        <v>-2.7</v>
       </c>
       <c r="E6" s="2">
-        <v>1.79</v>
+        <v>3.53</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="I6" s="2">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,16 +882,16 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>721.2</v>
+        <v>1259.1</v>
       </c>
       <c r="C7" s="2">
-        <v>-1.53</v>
+        <v>0.39</v>
       </c>
       <c r="D7" s="2">
-        <v>-2.91</v>
+        <v>2.46</v>
       </c>
       <c r="E7" s="2">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
@@ -900,10 +900,10 @@
         <v>80</v>
       </c>
       <c r="H7" s="2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I7" s="2">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>420.4</v>
+        <v>1761</v>
       </c>
       <c r="C8" s="2">
-        <v>-5.79</v>
+        <v>-1.96</v>
       </c>
       <c r="D8" s="2">
-        <v>0.9399999999999999</v>
+        <v>5.82</v>
       </c>
       <c r="E8" s="2">
-        <v>1.22</v>
+        <v>-0.4</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
+        <v>88</v>
+      </c>
+      <c r="H8" s="2">
+        <v>92</v>
+      </c>
+      <c r="I8" s="2">
         <v>94</v>
-      </c>
-      <c r="H8" s="2">
-        <v>60</v>
-      </c>
-      <c r="I8" s="2">
-        <v>84</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1533</v>
+        <v>1355</v>
       </c>
       <c r="C9" s="2">
-        <v>5.99</v>
+        <v>10.02</v>
       </c>
       <c r="D9" s="2">
-        <v>-1.7</v>
+        <v>-4.71</v>
       </c>
       <c r="E9" s="2">
-        <v>-4</v>
+        <v>-2.13</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H9" s="2">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="I9" s="2">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1243.1</v>
+        <v>1216.7</v>
       </c>
       <c r="C10" s="2">
-        <v>6.08</v>
+        <v>4.25</v>
       </c>
       <c r="D10" s="2">
-        <v>-2.2</v>
+        <v>-10.05</v>
       </c>
       <c r="E10" s="2">
-        <v>-3.89</v>
+        <v>0.8</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H10" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,16 +1010,16 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>4515.7</v>
+        <v>4833</v>
       </c>
       <c r="C11" s="2">
-        <v>11.18</v>
+        <v>7.11</v>
       </c>
       <c r="D11" s="2">
-        <v>-3.45</v>
+        <v>-7.6</v>
       </c>
       <c r="E11" s="2">
-        <v>-10.05</v>
+        <v>-2.26</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
@@ -1028,10 +1028,10 @@
         <v>96</v>
       </c>
       <c r="H11" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I11" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1344</v>
+        <v>1514.1</v>
       </c>
       <c r="C12" s="2">
-        <v>-3.17</v>
+        <v>5.51</v>
       </c>
       <c r="D12" s="2">
-        <v>-4.72</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="E12" s="2">
-        <v>-2.96</v>
+        <v>-0.77</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H12" s="2">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I12" s="2">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1217.1</v>
+        <v>266</v>
       </c>
       <c r="C13" s="2">
-        <v>-5.33</v>
+        <v>-3.97</v>
       </c>
       <c r="D13" s="2">
-        <v>-0.83</v>
+        <v>-6.68</v>
       </c>
       <c r="E13" s="2">
-        <v>-4.39</v>
+        <v>2.58</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I13" s="2">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1801</v>
+        <v>707.25</v>
       </c>
       <c r="C14" s="2">
-        <v>0.36</v>
+        <v>-4.6</v>
       </c>
       <c r="D14" s="2">
-        <v>-7.22</v>
+        <v>-6.19</v>
       </c>
       <c r="E14" s="2">
-        <v>-5.16</v>
+        <v>1.94</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="I14" s="2">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,25 +1138,25 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1233</v>
+        <v>1805.1</v>
       </c>
       <c r="C15" s="2">
-        <v>-2.97</v>
+        <v>0.2</v>
       </c>
       <c r="D15" s="2">
-        <v>-0.63</v>
+        <v>-7.75</v>
       </c>
       <c r="E15" s="2">
-        <v>-6.94</v>
+        <v>-1.84</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="H15" s="2">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="I15" s="2">
         <v>76</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>534.2</v>
+        <v>960</v>
       </c>
       <c r="C16" s="2">
-        <v>-9.869999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="D16" s="2">
-        <v>-3.76</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="E16" s="2">
-        <v>-2.23</v>
+        <v>-8</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="H16" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I16" s="2">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1310.6</v>
+        <v>10675</v>
       </c>
       <c r="C17" s="2">
-        <v>5.19</v>
+        <v>-1.87</v>
       </c>
       <c r="D17" s="2">
-        <v>-7.76</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="E17" s="2">
-        <v>-7.91</v>
+        <v>-2.77</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="H17" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I17" s="2">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>2816.8</v>
+        <v>959.1</v>
       </c>
       <c r="C18" s="2">
-        <v>-4.06</v>
+        <v>-1.17</v>
       </c>
       <c r="D18" s="2">
-        <v>-6.93</v>
+        <v>-6.46</v>
       </c>
       <c r="E18" s="2">
-        <v>-4.13</v>
+        <v>-5.01</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H18" s="2">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="I18" s="2">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>954.1</v>
+        <v>1684.6</v>
       </c>
       <c r="C19" s="2">
-        <v>-1.07</v>
+        <v>-5.58</v>
       </c>
       <c r="D19" s="2">
-        <v>-6</v>
+        <v>-10.27</v>
       </c>
       <c r="E19" s="2">
-        <v>-6.1</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="I19" s="2">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1721.6</v>
+        <v>411.55</v>
       </c>
       <c r="C20" s="2">
-        <v>-5.93</v>
+        <v>-10.58</v>
       </c>
       <c r="D20" s="2">
-        <v>-7.37</v>
+        <v>1.23</v>
       </c>
       <c r="E20" s="2">
-        <v>-3.01</v>
+        <v>-4.73</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="H20" s="2">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I20" s="2">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>8133.5</v>
+        <v>2156</v>
       </c>
       <c r="C21" s="2">
-        <v>-0.41</v>
+        <v>-3.3</v>
       </c>
       <c r="D21" s="2">
-        <v>-7.52</v>
+        <v>-11.34</v>
       </c>
       <c r="E21" s="2">
-        <v>-5.97</v>
+        <v>-2.18</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="H21" s="2">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="I21" s="2">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>948.3</v>
+        <v>940.45</v>
       </c>
       <c r="C22" s="2">
-        <v>5.05</v>
+        <v>3.59</v>
       </c>
       <c r="D22" s="2">
-        <v>-6.37</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="E22" s="2">
-        <v>-10.58</v>
+        <v>-9.4</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="H22" s="2">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="I22" s="2">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1741.1</v>
+        <v>1333</v>
       </c>
       <c r="C23" s="2">
-        <v>-3.61</v>
+        <v>-3.74</v>
       </c>
       <c r="D23" s="2">
-        <v>-8.279999999999999</v>
+        <v>-12.34</v>
       </c>
       <c r="E23" s="2">
-        <v>-5.38</v>
+        <v>-3.84</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H23" s="2">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="I23" s="2">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>383.1</v>
+        <v>1760</v>
       </c>
       <c r="C24" s="2">
-        <v>-6.6</v>
+        <v>-1.34</v>
       </c>
       <c r="D24" s="2">
-        <v>-5.28</v>
+        <v>-12.05</v>
       </c>
       <c r="E24" s="2">
-        <v>-5.49</v>
+        <v>-5.43</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="H24" s="2">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="I24" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,25 +1458,25 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>945</v>
+        <v>3703.3</v>
       </c>
       <c r="C25" s="2">
-        <v>0.34</v>
+        <v>-6.32</v>
       </c>
       <c r="D25" s="2">
-        <v>-5.98</v>
+        <v>-5.95</v>
       </c>
       <c r="E25" s="2">
-        <v>-9.220000000000001</v>
+        <v>-6.36</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="H25" s="2">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="I25" s="2">
         <v>50</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>940.95</v>
+        <v>4410</v>
       </c>
       <c r="C26" s="2">
-        <v>-2.33</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D26" s="2">
-        <v>-12.91</v>
+        <v>-9.07</v>
       </c>
       <c r="E26" s="2">
-        <v>-4.45</v>
+        <v>-12.17</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I26" s="2">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>10710</v>
+        <v>1301</v>
       </c>
       <c r="C27" s="2">
-        <v>-4.82</v>
+        <v>-4.51</v>
       </c>
       <c r="D27" s="2">
-        <v>-7.74</v>
+        <v>-11.28</v>
       </c>
       <c r="E27" s="2">
-        <v>-6.12</v>
+        <v>-5.26</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="I27" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>3693.4</v>
+        <v>7050</v>
       </c>
       <c r="C28" s="2">
-        <v>-9.4</v>
+        <v>-0.09</v>
       </c>
       <c r="D28" s="2">
-        <v>-2.44</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="E28" s="2">
-        <v>-6.83</v>
+        <v>-8.41</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H28" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I28" s="2">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1035</v>
+        <v>1023.4</v>
       </c>
       <c r="C29" s="2">
-        <v>-8.92</v>
+        <v>-14.48</v>
       </c>
       <c r="D29" s="2">
-        <v>-0.57</v>
+        <v>-11.4</v>
       </c>
       <c r="E29" s="2">
-        <v>-8.41</v>
+        <v>-1.26</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H29" s="2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I29" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>178</v>
+        <v>1734.7</v>
       </c>
       <c r="C30" s="2">
-        <v>-12.67</v>
+        <v>0.1</v>
       </c>
       <c r="D30" s="2">
-        <v>-2.56</v>
+        <v>-9.15</v>
       </c>
       <c r="E30" s="2">
-        <v>-5.72</v>
+        <v>-10.61</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="I30" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>255.9</v>
+        <v>1856.7</v>
       </c>
       <c r="C31" s="2">
-        <v>-10.81</v>
+        <v>-10.28</v>
       </c>
       <c r="D31" s="2">
-        <v>-9.720000000000001</v>
+        <v>-11.92</v>
       </c>
       <c r="E31" s="2">
-        <v>-3.1</v>
+        <v>-4.41</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="H31" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I31" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>2407</v>
+        <v>368.15</v>
       </c>
       <c r="C32" s="2">
-        <v>-9.119999999999999</v>
+        <v>-9.33</v>
       </c>
       <c r="D32" s="2">
-        <v>-8.75</v>
+        <v>-4.22</v>
       </c>
       <c r="E32" s="2">
-        <v>-4.76</v>
+        <v>-9.1</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="H32" s="2">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I32" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>6920</v>
+        <v>8027.5</v>
       </c>
       <c r="C33" s="2">
-        <v>-2.57</v>
+        <v>-3.06</v>
       </c>
       <c r="D33" s="2">
-        <v>-8.33</v>
+        <v>-10.58</v>
       </c>
       <c r="E33" s="2">
-        <v>-9.31</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H33" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="I33" s="2">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>941.85</v>
+        <v>214.62</v>
       </c>
       <c r="C34" s="2">
-        <v>-15.97</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="D34" s="2">
-        <v>-0.1</v>
+        <v>-12.89</v>
       </c>
       <c r="E34" s="2">
-        <v>-6.84</v>
+        <v>-6.79</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H34" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I34" s="2">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>2962</v>
+        <v>1170.3</v>
       </c>
       <c r="C35" s="2">
-        <v>-4.84</v>
+        <v>-10.47</v>
       </c>
       <c r="D35" s="2">
-        <v>-3.83</v>
+        <v>-9.48</v>
       </c>
       <c r="E35" s="2">
-        <v>-10.84</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="H35" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1307.7</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2">
-        <v>-7.56</v>
+        <v>-14.02</v>
       </c>
       <c r="D36" s="2">
-        <v>-9.41</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="E36" s="2">
-        <v>-7.29</v>
+        <v>-6.87</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H36" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I36" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>254.55</v>
+        <v>162.57</v>
       </c>
       <c r="C37" s="2">
-        <v>-11.98</v>
+        <v>-19.44</v>
       </c>
       <c r="D37" s="2">
-        <v>-11.26</v>
+        <v>-12.75</v>
       </c>
       <c r="E37" s="2">
-        <v>-4.3</v>
+        <v>-2.24</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="H37" s="2">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="I37" s="2">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>2860</v>
+        <v>173.8</v>
       </c>
       <c r="C38" s="2">
-        <v>-5.11</v>
+        <v>-16.28</v>
       </c>
       <c r="D38" s="2">
-        <v>-9.529999999999999</v>
+        <v>-7.02</v>
       </c>
       <c r="E38" s="2">
-        <v>-9.779999999999999</v>
+        <v>-6.95</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="H38" s="2">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="I38" s="2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>1732.6</v>
+        <v>955</v>
       </c>
       <c r="C39" s="2">
-        <v>-2.78</v>
+        <v>-16.52</v>
       </c>
       <c r="D39" s="2">
-        <v>-7.68</v>
+        <v>-12.72</v>
       </c>
       <c r="E39" s="2">
-        <v>-12.05</v>
+        <v>-4.46</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H39" s="2">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="I39" s="2">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>2075</v>
+        <v>221.27</v>
       </c>
       <c r="C40" s="2">
-        <v>-7.64</v>
+        <v>-17.01</v>
       </c>
       <c r="D40" s="2">
-        <v>-7.95</v>
+        <v>-8.02</v>
       </c>
       <c r="E40" s="2">
-        <v>-9.94</v>
+        <v>-6.74</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H40" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I40" s="2">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,16 +1970,16 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>315.1</v>
+        <v>2339.1</v>
       </c>
       <c r="C41" s="2">
-        <v>-17.68</v>
+        <v>-11.38</v>
       </c>
       <c r="D41" s="2">
-        <v>-8.27</v>
+        <v>-14.82</v>
       </c>
       <c r="E41" s="2">
-        <v>-5.23</v>
+        <v>-6.36</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
@@ -1988,10 +1988,10 @@
         <v>42</v>
       </c>
       <c r="H41" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I41" s="2">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>222.37</v>
+        <v>2890</v>
       </c>
       <c r="C42" s="2">
-        <v>-15.86</v>
+        <v>-6.53</v>
       </c>
       <c r="D42" s="2">
-        <v>-10.23</v>
+        <v>-6.63</v>
       </c>
       <c r="E42" s="2">
-        <v>-5.23</v>
+        <v>-12.93</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H42" s="2">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="I42" s="2">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>2580</v>
+        <v>1168</v>
       </c>
       <c r="C43" s="2">
-        <v>-8.25</v>
+        <v>-10.53</v>
       </c>
       <c r="D43" s="2">
-        <v>-10.74</v>
+        <v>-8.09</v>
       </c>
       <c r="E43" s="2">
-        <v>-9.57</v>
+        <v>-10.43</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="H43" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I43" s="2">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>957</v>
+        <v>249.15</v>
       </c>
       <c r="C44" s="2">
-        <v>-18.79</v>
+        <v>-12.19</v>
       </c>
       <c r="D44" s="2">
-        <v>-12.04</v>
+        <v>-12.39</v>
       </c>
       <c r="E44" s="2">
-        <v>-5.25</v>
+        <v>-8.32</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H44" s="2">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="I44" s="2">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>1836</v>
+        <v>2796.2</v>
       </c>
       <c r="C45" s="2">
-        <v>-13.88</v>
+        <v>-6.16</v>
       </c>
       <c r="D45" s="2">
-        <v>-14.41</v>
+        <v>-14.85</v>
       </c>
       <c r="E45" s="2">
-        <v>-6.96</v>
+        <v>-10.49</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H45" s="2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I45" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>212.5</v>
+        <v>11420</v>
       </c>
       <c r="C46" s="2">
-        <v>-10.86</v>
+        <v>-11.57</v>
       </c>
       <c r="D46" s="2">
-        <v>-9.25</v>
+        <v>-18.7</v>
       </c>
       <c r="E46" s="2">
-        <v>-11.27</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H46" s="2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I46" s="2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>1167.7</v>
+        <v>900.35</v>
       </c>
       <c r="C47" s="2">
+        <v>-20.53</v>
+      </c>
+      <c r="D47" s="2">
+        <v>-7.22</v>
+      </c>
+      <c r="E47" s="2">
         <v>-11.21</v>
-      </c>
-      <c r="D47" s="2">
-        <v>-8.630000000000001</v>
-      </c>
-      <c r="E47" s="2">
-        <v>-11.67</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H47" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I47" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>10045</v>
+        <v>2634.4</v>
       </c>
       <c r="C48" s="2">
-        <v>-3.97</v>
+        <v>-9.91</v>
       </c>
       <c r="D48" s="2">
-        <v>-9.75</v>
+        <v>-13.6</v>
       </c>
       <c r="E48" s="2">
-        <v>-15.72</v>
+        <v>-14.39</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="H48" s="2">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="I48" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>11386</v>
+        <v>9778</v>
       </c>
       <c r="C49" s="2">
-        <v>-12.39</v>
+        <v>-4.69</v>
       </c>
       <c r="D49" s="2">
-        <v>-14.44</v>
+        <v>-14.47</v>
       </c>
       <c r="E49" s="2">
-        <v>-10.3</v>
+        <v>-16.91</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H49" s="2">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="I49" s="2">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,16 +2258,16 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>159.35</v>
+        <v>279.9</v>
       </c>
       <c r="C50" s="2">
-        <v>-21.09</v>
+        <v>-29.12</v>
       </c>
       <c r="D50" s="2">
-        <v>-9.01</v>
+        <v>-16.25</v>
       </c>
       <c r="E50" s="2">
-        <v>-9.67</v>
+        <v>-6.86</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
@@ -2276,10 +2276,10 @@
         <v>2</v>
       </c>
       <c r="H50" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I50" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>279.4</v>
+        <v>883.8</v>
       </c>
       <c r="C51" s="2">
-        <v>-28.48</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="D51" s="2">
-        <v>-13.71</v>
+        <v>-21.43</v>
       </c>
       <c r="E51" s="2">
-        <v>-10.3</v>
+        <v>-14.9</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="H51" s="2">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="I51" s="2">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2462,28 +2462,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>313.9</v>
+        <v>441</v>
       </c>
       <c r="C2" s="2">
-        <v>25.27</v>
+        <v>15.95</v>
       </c>
       <c r="D2" s="2">
-        <v>12.11</v>
+        <v>13.25</v>
       </c>
       <c r="E2" s="2">
-        <v>-2.74</v>
+        <v>5.87</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="I2" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2491,115 +2491,115 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>418.35</v>
+        <v>323.45</v>
       </c>
       <c r="C3" s="2">
-        <v>9.08</v>
+        <v>30.95</v>
       </c>
       <c r="D3" s="2">
-        <v>8.73</v>
+        <v>4.12</v>
       </c>
       <c r="E3" s="2">
-        <v>-1.45</v>
+        <v>0.42</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1">
-        <v>1737.8</v>
+        <v>1761</v>
       </c>
       <c r="C4" s="2">
-        <v>-3.3</v>
+        <v>-1.96</v>
       </c>
       <c r="D4" s="2">
-        <v>-1.72</v>
+        <v>5.82</v>
       </c>
       <c r="E4" s="2">
-        <v>1.79</v>
+        <v>-0.4</v>
       </c>
       <c r="F4" s="2">
+        <v>88</v>
+      </c>
+      <c r="G4" s="2">
+        <v>88</v>
+      </c>
+      <c r="H4" s="2">
         <v>92</v>
       </c>
-      <c r="G4" s="2">
-        <v>98</v>
-      </c>
-      <c r="H4" s="2">
-        <v>98</v>
-      </c>
       <c r="I4" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1">
-        <v>1533</v>
+        <v>1216.7</v>
       </c>
       <c r="C5" s="2">
-        <v>5.99</v>
+        <v>4.25</v>
       </c>
       <c r="D5" s="2">
-        <v>-1.7</v>
+        <v>-10.05</v>
       </c>
       <c r="E5" s="2">
-        <v>-4</v>
+        <v>0.8</v>
       </c>
       <c r="F5" s="2">
+        <v>84</v>
+      </c>
+      <c r="G5" s="2">
         <v>86</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
+        <v>86</v>
+      </c>
+      <c r="I5" s="2">
         <v>84</v>
-      </c>
-      <c r="H5" s="2">
-        <v>82</v>
-      </c>
-      <c r="I5" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1">
-        <v>4515.7</v>
+        <v>1514.1</v>
       </c>
       <c r="C6" s="2">
-        <v>11.18</v>
+        <v>5.51</v>
       </c>
       <c r="D6" s="2">
-        <v>-3.45</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="E6" s="2">
-        <v>-10.05</v>
+        <v>-0.77</v>
       </c>
       <c r="F6" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G6" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2">
+        <v>80</v>
+      </c>
+      <c r="I6" s="2">
         <v>88</v>
-      </c>
-      <c r="I6" s="2">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2695,28 +2695,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>313.9</v>
+        <v>441</v>
       </c>
       <c r="C2" s="2">
-        <v>25.27</v>
+        <v>15.95</v>
       </c>
       <c r="D2" s="2">
-        <v>12.11</v>
+        <v>13.25</v>
       </c>
       <c r="E2" s="2">
-        <v>-2.74</v>
+        <v>5.87</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="I2" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2724,57 +2724,57 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>418.35</v>
+        <v>323.45</v>
       </c>
       <c r="C3" s="2">
-        <v>9.08</v>
+        <v>30.95</v>
       </c>
       <c r="D3" s="2">
-        <v>8.73</v>
+        <v>4.12</v>
       </c>
       <c r="E3" s="2">
-        <v>-1.45</v>
+        <v>0.42</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1737.8</v>
+        <v>1197</v>
       </c>
       <c r="C4" s="2">
-        <v>-3.3</v>
+        <v>-4.65</v>
       </c>
       <c r="D4" s="2">
-        <v>-1.72</v>
+        <v>4.56</v>
       </c>
       <c r="E4" s="2">
-        <v>1.79</v>
+        <v>4.72</v>
       </c>
       <c r="F4" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="I4" s="2">
-        <v>82</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2782,16 +2782,16 @@
         <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>721.2</v>
+        <v>1259.1</v>
       </c>
       <c r="C5" s="2">
-        <v>-1.53</v>
+        <v>0.39</v>
       </c>
       <c r="D5" s="2">
-        <v>-2.91</v>
+        <v>2.46</v>
       </c>
       <c r="E5" s="2">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="F5" s="2">
         <v>90</v>
@@ -2800,10 +2800,10 @@
         <v>80</v>
       </c>
       <c r="H5" s="2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I5" s="2">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2811,115 +2811,115 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>420.4</v>
+        <v>1761</v>
       </c>
       <c r="C6" s="2">
-        <v>-5.79</v>
+        <v>-1.96</v>
       </c>
       <c r="D6" s="2">
-        <v>0.9399999999999999</v>
+        <v>5.82</v>
       </c>
       <c r="E6" s="2">
-        <v>1.22</v>
+        <v>-0.4</v>
       </c>
       <c r="F6" s="2">
         <v>88</v>
       </c>
       <c r="G6" s="2">
+        <v>88</v>
+      </c>
+      <c r="H6" s="2">
+        <v>92</v>
+      </c>
+      <c r="I6" s="2">
         <v>94</v>
-      </c>
-      <c r="H6" s="2">
-        <v>60</v>
-      </c>
-      <c r="I6" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>1533</v>
+        <v>1216.7</v>
       </c>
       <c r="C7" s="2">
-        <v>5.99</v>
+        <v>4.25</v>
       </c>
       <c r="D7" s="2">
-        <v>-1.7</v>
+        <v>-10.05</v>
       </c>
       <c r="E7" s="2">
-        <v>-4</v>
+        <v>0.8</v>
       </c>
       <c r="F7" s="2">
+        <v>84</v>
+      </c>
+      <c r="G7" s="2">
         <v>86</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>86</v>
+      </c>
+      <c r="I7" s="2">
         <v>84</v>
-      </c>
-      <c r="H7" s="2">
-        <v>82</v>
-      </c>
-      <c r="I7" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1">
-        <v>1243.1</v>
+        <v>4833</v>
       </c>
       <c r="C8" s="2">
-        <v>6.08</v>
+        <v>7.11</v>
       </c>
       <c r="D8" s="2">
-        <v>-2.2</v>
+        <v>-7.6</v>
       </c>
       <c r="E8" s="2">
-        <v>-3.89</v>
+        <v>-2.26</v>
       </c>
       <c r="F8" s="2">
+        <v>82</v>
+      </c>
+      <c r="G8" s="2">
+        <v>96</v>
+      </c>
+      <c r="H8" s="2">
         <v>84</v>
       </c>
-      <c r="G8" s="2">
-        <v>90</v>
-      </c>
-      <c r="H8" s="2">
-        <v>78</v>
-      </c>
       <c r="I8" s="2">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1">
-        <v>4515.7</v>
+        <v>1514.1</v>
       </c>
       <c r="C9" s="2">
-        <v>11.18</v>
+        <v>5.51</v>
       </c>
       <c r="D9" s="2">
-        <v>-3.45</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="E9" s="2">
-        <v>-10.05</v>
+        <v>-0.77</v>
       </c>
       <c r="F9" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G9" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2">
+        <v>80</v>
+      </c>
+      <c r="I9" s="2">
         <v>88</v>
-      </c>
-      <c r="I9" s="2">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2998,13 +2998,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3012,13 +3012,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2">
         <v>16</v>
-      </c>
-      <c r="D3" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3026,7 +3026,7 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2">
         <v>16</v>
@@ -3040,13 +3040,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-10-09</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-10-09</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-10-09</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-10-09</t>
+    <t>Price_2026-10-16</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-10-16</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-10-16</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-10-16</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-10-16</t>
   </si>
   <si>
     <t>RS_Score_2026-10-09</t>
@@ -43,7 +46,13 @@
     <t>RS_Score_2026-09-25</t>
   </si>
   <si>
-    <t>RS_Score_2026-09-18</t>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
   </si>
   <si>
     <t>KOTAKBANK</t>
@@ -52,144 +61,135 @@
     <t>ETERNAL</t>
   </si>
   <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
     <t>HDFCLIFE</t>
   </si>
   <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
   </si>
   <si>
     <t>ADANIPORTS</t>
   </si>
   <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
   </si>
   <si>
     <t>INDIGO</t>
   </si>
   <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>BEL</t>
   </si>
   <si>
     <t>SBIN</t>
   </si>
   <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
     <t>SBILIFE</t>
   </si>
   <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>TCS</t>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>SHRIRAMFIN</t>
   </si>
   <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>ADANIENT</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
     <t>NESTLEIND</t>
   </si>
   <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>ADANIENT</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
     <t>TMPV</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
     <t>2026-10-09</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>441</v>
+        <v>1790</v>
       </c>
       <c r="C2" s="2">
-        <v>15.95</v>
+        <v>24.18</v>
       </c>
       <c r="D2" s="2">
-        <v>13.25</v>
+        <v>9.67</v>
       </c>
       <c r="E2" s="2">
-        <v>5.87</v>
+        <v>16.45</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>323.45</v>
+        <v>2465</v>
       </c>
       <c r="C3" s="2">
-        <v>30.95</v>
+        <v>15.68</v>
       </c>
       <c r="D3" s="2">
-        <v>4.12</v>
+        <v>4.43</v>
       </c>
       <c r="E3" s="2">
-        <v>0.42</v>
+        <v>17.72</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="H3" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>556.65</v>
+        <v>1380</v>
       </c>
       <c r="C4" s="2">
-        <v>-2.74</v>
+        <v>24.24</v>
       </c>
       <c r="D4" s="2">
-        <v>2.06</v>
+        <v>4.29</v>
       </c>
       <c r="E4" s="2">
-        <v>5.8</v>
+        <v>11.45</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1197</v>
+        <v>447.4</v>
       </c>
       <c r="C5" s="2">
-        <v>-4.65</v>
+        <v>15.48</v>
       </c>
       <c r="D5" s="2">
-        <v>4.56</v>
+        <v>13.55</v>
       </c>
       <c r="E5" s="2">
-        <v>4.72</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>2918.2</v>
+        <v>325.3</v>
       </c>
       <c r="C6" s="2">
-        <v>2.96</v>
+        <v>35.65</v>
       </c>
       <c r="D6" s="2">
-        <v>-2.7</v>
+        <v>2.86</v>
       </c>
       <c r="E6" s="2">
-        <v>3.53</v>
+        <v>-0.47</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="H6" s="2">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1259.1</v>
+        <v>184.4</v>
       </c>
       <c r="C7" s="2">
-        <v>0.39</v>
+        <v>4.23</v>
       </c>
       <c r="D7" s="2">
-        <v>2.46</v>
+        <v>-0.92</v>
       </c>
       <c r="E7" s="2">
-        <v>1.05</v>
+        <v>10.53</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="I7" s="2">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1761</v>
+        <v>1161.2</v>
       </c>
       <c r="C8" s="2">
-        <v>-1.96</v>
+        <v>1.39</v>
       </c>
       <c r="D8" s="2">
-        <v>5.82</v>
+        <v>-0.33</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.4</v>
+        <v>10.44</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1355</v>
+        <v>1397</v>
       </c>
       <c r="C9" s="2">
-        <v>10.02</v>
+        <v>8.93</v>
       </c>
       <c r="D9" s="2">
-        <v>-4.71</v>
+        <v>-4.15</v>
       </c>
       <c r="E9" s="2">
-        <v>-2.13</v>
+        <v>4.34</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
+        <v>86</v>
+      </c>
+      <c r="H9" s="2">
         <v>66</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>52</v>
-      </c>
-      <c r="I9" s="2">
-        <v>62</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1216.7</v>
+        <v>2958.7</v>
       </c>
       <c r="C10" s="2">
-        <v>4.25</v>
+        <v>7.56</v>
       </c>
       <c r="D10" s="2">
-        <v>-10.05</v>
+        <v>-4.78</v>
       </c>
       <c r="E10" s="2">
-        <v>0.8</v>
+        <v>4.77</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="I10" s="2">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>4833</v>
+        <v>1905</v>
       </c>
       <c r="C11" s="2">
-        <v>7.11</v>
+        <v>8.66</v>
       </c>
       <c r="D11" s="2">
-        <v>-7.6</v>
+        <v>-2.21</v>
       </c>
       <c r="E11" s="2">
-        <v>-2.26</v>
+        <v>0.62</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="H11" s="2">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="I11" s="2">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1514.1</v>
+        <v>1218.8</v>
       </c>
       <c r="C12" s="2">
-        <v>5.51</v>
+        <v>-3.55</v>
       </c>
       <c r="D12" s="2">
-        <v>-9.279999999999999</v>
+        <v>4.08</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.77</v>
+        <v>2.85</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I12" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>266</v>
+        <v>1290</v>
       </c>
       <c r="C13" s="2">
-        <v>-3.97</v>
+        <v>-1.79</v>
       </c>
       <c r="D13" s="2">
-        <v>-6.68</v>
+        <v>2.71</v>
       </c>
       <c r="E13" s="2">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I13" s="2">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>707.25</v>
+        <v>553</v>
       </c>
       <c r="C14" s="2">
-        <v>-4.6</v>
+        <v>0.99</v>
       </c>
       <c r="D14" s="2">
-        <v>-6.19</v>
+        <v>1.94</v>
       </c>
       <c r="E14" s="2">
-        <v>1.94</v>
+        <v>0.37</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H14" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1805.1</v>
+        <v>417.2</v>
       </c>
       <c r="C15" s="2">
-        <v>0.2</v>
+        <v>-5.07</v>
       </c>
       <c r="D15" s="2">
-        <v>-7.75</v>
+        <v>1.66</v>
       </c>
       <c r="E15" s="2">
-        <v>-1.84</v>
+        <v>1.78</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="H15" s="2">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="I15" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>960</v>
+        <v>728.85</v>
       </c>
       <c r="C16" s="2">
-        <v>10.16</v>
+        <v>-0.8</v>
       </c>
       <c r="D16" s="2">
-        <v>-8.880000000000001</v>
+        <v>-0.74</v>
       </c>
       <c r="E16" s="2">
-        <v>-8</v>
+        <v>-0.29</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="I16" s="2">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>10675</v>
+        <v>1743.2</v>
       </c>
       <c r="C17" s="2">
-        <v>-1.87</v>
+        <v>-3.88</v>
       </c>
       <c r="D17" s="2">
-        <v>-9.890000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="E17" s="2">
-        <v>-2.77</v>
+        <v>-4.43</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="I17" s="2">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>959.1</v>
+        <v>10862</v>
       </c>
       <c r="C18" s="2">
-        <v>-1.17</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>-6.46</v>
+        <v>-10.05</v>
       </c>
       <c r="E18" s="2">
-        <v>-5.01</v>
+        <v>-1.38</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H18" s="2">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="I18" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1684.6</v>
+        <v>982.1</v>
       </c>
       <c r="C19" s="2">
-        <v>-5.58</v>
+        <v>11.77</v>
       </c>
       <c r="D19" s="2">
-        <v>-10.27</v>
+        <v>-14.21</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.9399999999999999</v>
+        <v>-5.59</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H19" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I19" s="2">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,25 +1298,25 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>411.55</v>
+        <v>263.5</v>
       </c>
       <c r="C20" s="2">
-        <v>-10.58</v>
+        <v>-7.1</v>
       </c>
       <c r="D20" s="2">
-        <v>1.23</v>
+        <v>-7.83</v>
       </c>
       <c r="E20" s="2">
-        <v>-4.73</v>
+        <v>0.46</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="I20" s="2">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>2156</v>
+        <v>1211.2</v>
       </c>
       <c r="C21" s="2">
-        <v>-3.3</v>
+        <v>-3.78</v>
       </c>
       <c r="D21" s="2">
-        <v>-11.34</v>
+        <v>-8.59</v>
       </c>
       <c r="E21" s="2">
-        <v>-2.18</v>
+        <v>-1.24</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H21" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I21" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>940.45</v>
+        <v>4444.8</v>
       </c>
       <c r="C22" s="2">
-        <v>3.59</v>
+        <v>10.32</v>
       </c>
       <c r="D22" s="2">
-        <v>-8.449999999999999</v>
+        <v>-11.07</v>
       </c>
       <c r="E22" s="2">
-        <v>-9.4</v>
+        <v>-7.37</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="I22" s="2">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1333</v>
+        <v>7225</v>
       </c>
       <c r="C23" s="2">
-        <v>-3.74</v>
+        <v>1.12</v>
       </c>
       <c r="D23" s="2">
-        <v>-12.34</v>
+        <v>-9.32</v>
       </c>
       <c r="E23" s="2">
-        <v>-3.84</v>
+        <v>-3.87</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H23" s="2">
         <v>30</v>
       </c>
       <c r="I23" s="2">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1760</v>
+        <v>4686.9</v>
       </c>
       <c r="C24" s="2">
-        <v>-1.34</v>
+        <v>3.58</v>
       </c>
       <c r="D24" s="2">
-        <v>-12.05</v>
+        <v>-11.88</v>
       </c>
       <c r="E24" s="2">
-        <v>-5.43</v>
+        <v>-4.74</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="I24" s="2">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,16 +1458,16 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>3703.3</v>
+        <v>1764</v>
       </c>
       <c r="C25" s="2">
-        <v>-6.32</v>
+        <v>-1</v>
       </c>
       <c r="D25" s="2">
-        <v>-5.95</v>
+        <v>-9.58</v>
       </c>
       <c r="E25" s="2">
-        <v>-6.36</v>
+        <v>-3.99</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
@@ -1476,10 +1476,10 @@
         <v>56</v>
       </c>
       <c r="H25" s="2">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="I25" s="2">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>4410</v>
+        <v>1216.3</v>
       </c>
       <c r="C26" s="2">
-        <v>8.210000000000001</v>
+        <v>-3.66</v>
       </c>
       <c r="D26" s="2">
-        <v>-9.07</v>
+        <v>-7</v>
       </c>
       <c r="E26" s="2">
-        <v>-12.17</v>
+        <v>-4.65</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="H26" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="I26" s="2">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1301</v>
+        <v>376.85</v>
       </c>
       <c r="C27" s="2">
-        <v>-4.51</v>
+        <v>-7.59</v>
       </c>
       <c r="D27" s="2">
-        <v>-11.28</v>
+        <v>-5.47</v>
       </c>
       <c r="E27" s="2">
-        <v>-5.26</v>
+        <v>-4.18</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="I27" s="2">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>7050</v>
+        <v>962.6</v>
       </c>
       <c r="C28" s="2">
-        <v>-0.09</v>
+        <v>-4.05</v>
       </c>
       <c r="D28" s="2">
-        <v>-9.970000000000001</v>
+        <v>-11.28</v>
       </c>
       <c r="E28" s="2">
-        <v>-8.41</v>
+        <v>-3.37</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="H28" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I28" s="2">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1023.4</v>
+        <v>315.15</v>
       </c>
       <c r="C29" s="2">
-        <v>-14.48</v>
+        <v>-9.41</v>
       </c>
       <c r="D29" s="2">
-        <v>-11.4</v>
+        <v>-7.67</v>
       </c>
       <c r="E29" s="2">
-        <v>-1.26</v>
+        <v>-2.63</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H29" s="2">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I29" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>1734.7</v>
+        <v>2920.9</v>
       </c>
       <c r="C30" s="2">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="D30" s="2">
-        <v>-9.15</v>
+        <v>-14.24</v>
       </c>
       <c r="E30" s="2">
-        <v>-10.61</v>
+        <v>-4.3</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H30" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I30" s="2">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>1856.7</v>
+        <v>1328</v>
       </c>
       <c r="C31" s="2">
-        <v>-10.28</v>
+        <v>-3.56</v>
       </c>
       <c r="D31" s="2">
-        <v>-11.92</v>
+        <v>-10.09</v>
       </c>
       <c r="E31" s="2">
-        <v>-4.41</v>
+        <v>-4.77</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="H31" s="2">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="I31" s="2">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>368.15</v>
+        <v>1656.8</v>
       </c>
       <c r="C32" s="2">
-        <v>-9.33</v>
+        <v>-4.16</v>
       </c>
       <c r="D32" s="2">
-        <v>-4.22</v>
+        <v>-11</v>
       </c>
       <c r="E32" s="2">
-        <v>-9.1</v>
+        <v>-4.29</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H32" s="2">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="I32" s="2">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>8027.5</v>
+        <v>1893.8</v>
       </c>
       <c r="C33" s="2">
-        <v>-3.06</v>
+        <v>-11.82</v>
       </c>
       <c r="D33" s="2">
-        <v>-10.58</v>
+        <v>-8.93</v>
       </c>
       <c r="E33" s="2">
-        <v>-9.800000000000001</v>
+        <v>-1.98</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H33" s="2">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="I33" s="2">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>214.62</v>
+        <v>978.9</v>
       </c>
       <c r="C34" s="2">
-        <v>-8.470000000000001</v>
+        <v>-11.65</v>
       </c>
       <c r="D34" s="2">
-        <v>-12.89</v>
+        <v>-10.19</v>
       </c>
       <c r="E34" s="2">
-        <v>-6.79</v>
+        <v>-1.72</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H34" s="2">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1170.3</v>
+        <v>10405</v>
       </c>
       <c r="C35" s="2">
-        <v>-10.47</v>
+        <v>2.57</v>
       </c>
       <c r="D35" s="2">
-        <v>-9.48</v>
+        <v>-10.46</v>
       </c>
       <c r="E35" s="2">
-        <v>-8.140000000000001</v>
+        <v>-8.84</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H35" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I35" s="2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>312</v>
+        <v>939.95</v>
       </c>
       <c r="C36" s="2">
-        <v>-14.02</v>
+        <v>5.34</v>
       </c>
       <c r="D36" s="2">
-        <v>-8.550000000000001</v>
+        <v>-17.62</v>
       </c>
       <c r="E36" s="2">
-        <v>-6.87</v>
+        <v>-6.94</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="H36" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I36" s="2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>162.57</v>
+        <v>1729</v>
       </c>
       <c r="C37" s="2">
-        <v>-19.44</v>
+        <v>3.98</v>
       </c>
       <c r="D37" s="2">
-        <v>-12.75</v>
+        <v>-17.11</v>
       </c>
       <c r="E37" s="2">
-        <v>-2.24</v>
+        <v>-6.67</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H37" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I37" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>173.8</v>
+        <v>222</v>
       </c>
       <c r="C38" s="2">
-        <v>-16.28</v>
+        <v>-11.49</v>
       </c>
       <c r="D38" s="2">
-        <v>-7.02</v>
+        <v>-6.25</v>
       </c>
       <c r="E38" s="2">
-        <v>-6.95</v>
+        <v>-4.64</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="H38" s="2">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="I38" s="2">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>955</v>
+        <v>175.5</v>
       </c>
       <c r="C39" s="2">
-        <v>-16.52</v>
+        <v>-10.13</v>
       </c>
       <c r="D39" s="2">
-        <v>-12.72</v>
+        <v>-7.29</v>
       </c>
       <c r="E39" s="2">
-        <v>-4.46</v>
+        <v>-5.41</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H39" s="2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I39" s="2">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>221.27</v>
+        <v>3627.1</v>
       </c>
       <c r="C40" s="2">
-        <v>-17.01</v>
+        <v>-7.41</v>
       </c>
       <c r="D40" s="2">
-        <v>-8.02</v>
+        <v>-10.7</v>
       </c>
       <c r="E40" s="2">
-        <v>-6.74</v>
+        <v>-6.64</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="H40" s="2">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="I40" s="2">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>2339.1</v>
+        <v>250.45</v>
       </c>
       <c r="C41" s="2">
-        <v>-11.38</v>
+        <v>-12.39</v>
       </c>
       <c r="D41" s="2">
-        <v>-14.82</v>
+        <v>-7.07</v>
       </c>
       <c r="E41" s="2">
-        <v>-6.36</v>
+        <v>-7.34</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H41" s="2">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I41" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,16 +2002,16 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>2890</v>
+        <v>216.25</v>
       </c>
       <c r="C42" s="2">
-        <v>-6.53</v>
+        <v>-5.83</v>
       </c>
       <c r="D42" s="2">
-        <v>-6.63</v>
+        <v>-17.61</v>
       </c>
       <c r="E42" s="2">
-        <v>-12.93</v>
+        <v>-5.93</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
@@ -2020,10 +2020,10 @@
         <v>36</v>
       </c>
       <c r="H42" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I42" s="2">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1168</v>
+        <v>2885.9</v>
       </c>
       <c r="C43" s="2">
-        <v>-10.53</v>
+        <v>-5.74</v>
       </c>
       <c r="D43" s="2">
-        <v>-8.09</v>
+        <v>-10.1</v>
       </c>
       <c r="E43" s="2">
-        <v>-10.43</v>
+        <v>-10.07</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="H43" s="2">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="I43" s="2">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>249.15</v>
+        <v>2331.9</v>
       </c>
       <c r="C44" s="2">
-        <v>-12.19</v>
+        <v>-13.37</v>
       </c>
       <c r="D44" s="2">
-        <v>-12.39</v>
+        <v>-15.36</v>
       </c>
       <c r="E44" s="2">
-        <v>-8.32</v>
+        <v>-4.87</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H44" s="2">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I44" s="2">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>2796.2</v>
+        <v>908</v>
       </c>
       <c r="C45" s="2">
-        <v>-6.16</v>
+        <v>-12.18</v>
       </c>
       <c r="D45" s="2">
-        <v>-14.85</v>
+        <v>-11.59</v>
       </c>
       <c r="E45" s="2">
-        <v>-10.49</v>
+        <v>-7.96</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H45" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I45" s="2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>11420</v>
+        <v>2700</v>
       </c>
       <c r="C46" s="2">
-        <v>-11.57</v>
+        <v>-7.84</v>
       </c>
       <c r="D46" s="2">
-        <v>-18.7</v>
+        <v>-10.77</v>
       </c>
       <c r="E46" s="2">
-        <v>-9.289999999999999</v>
+        <v>-10.6</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H46" s="2">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="I46" s="2">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>900.35</v>
+        <v>11445</v>
       </c>
       <c r="C47" s="2">
-        <v>-20.53</v>
+        <v>-11.57</v>
       </c>
       <c r="D47" s="2">
-        <v>-7.22</v>
+        <v>-17.9</v>
       </c>
       <c r="E47" s="2">
-        <v>-11.21</v>
+        <v>-5.44</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H47" s="2">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="I47" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>2634.4</v>
+        <v>7890</v>
       </c>
       <c r="C48" s="2">
-        <v>-9.91</v>
+        <v>-6.94</v>
       </c>
       <c r="D48" s="2">
-        <v>-13.6</v>
+        <v>-11.98</v>
       </c>
       <c r="E48" s="2">
-        <v>-14.39</v>
+        <v>-11.79</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="H48" s="2">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I48" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>9778</v>
+        <v>1265.5</v>
       </c>
       <c r="C49" s="2">
-        <v>-4.69</v>
+        <v>-11.59</v>
       </c>
       <c r="D49" s="2">
-        <v>-14.47</v>
+        <v>-17.56</v>
       </c>
       <c r="E49" s="2">
-        <v>-16.91</v>
+        <v>-7.79</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="H49" s="2">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="I49" s="2">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>279.9</v>
+        <v>286.85</v>
       </c>
       <c r="C50" s="2">
-        <v>-29.12</v>
+        <v>-24.09</v>
       </c>
       <c r="D50" s="2">
-        <v>-16.25</v>
+        <v>-16.94</v>
       </c>
       <c r="E50" s="2">
-        <v>-6.86</v>
+        <v>-5.58</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H50" s="2">
         <v>2</v>
       </c>
       <c r="I50" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>883.8</v>
+        <v>846</v>
       </c>
       <c r="C51" s="2">
-        <v>-8.300000000000001</v>
+        <v>-16.1</v>
       </c>
       <c r="D51" s="2">
-        <v>-21.43</v>
+        <v>-21.11</v>
       </c>
       <c r="E51" s="2">
-        <v>-14.9</v>
+        <v>-19.37</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
+        <v>2</v>
+      </c>
+      <c r="H51" s="2">
         <v>38</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>54</v>
-      </c>
-      <c r="I51" s="2">
-        <v>80</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2462,148 +2462,119 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>441</v>
+        <v>1790</v>
       </c>
       <c r="C2" s="2">
-        <v>15.95</v>
+        <v>24.18</v>
       </c>
       <c r="D2" s="2">
-        <v>13.25</v>
+        <v>9.67</v>
       </c>
       <c r="E2" s="2">
-        <v>5.87</v>
+        <v>16.45</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>323.45</v>
+        <v>1380</v>
       </c>
       <c r="C3" s="2">
-        <v>30.95</v>
+        <v>24.24</v>
       </c>
       <c r="D3" s="2">
-        <v>4.12</v>
+        <v>4.29</v>
       </c>
       <c r="E3" s="2">
-        <v>0.42</v>
+        <v>11.45</v>
       </c>
       <c r="F3" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G3" s="2">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1761</v>
+        <v>447.4</v>
       </c>
       <c r="C4" s="2">
-        <v>-1.96</v>
+        <v>15.48</v>
       </c>
       <c r="D4" s="2">
-        <v>5.82</v>
+        <v>13.55</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.4</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F4" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G4" s="2">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>1216.7</v>
+        <v>325.3</v>
       </c>
       <c r="C5" s="2">
-        <v>4.25</v>
+        <v>35.65</v>
       </c>
       <c r="D5" s="2">
-        <v>-10.05</v>
+        <v>2.86</v>
       </c>
       <c r="E5" s="2">
-        <v>0.8</v>
+        <v>-0.47</v>
       </c>
       <c r="F5" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H5" s="2">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1514.1</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5.51</v>
-      </c>
-      <c r="D6" s="2">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="E6" s="2">
-        <v>-0.77</v>
-      </c>
-      <c r="F6" s="2">
-        <v>80</v>
-      </c>
-      <c r="G6" s="2">
-        <v>92</v>
-      </c>
-      <c r="H6" s="2">
-        <v>80</v>
-      </c>
-      <c r="I6" s="2">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C5">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2611,7 +2582,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D5">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2619,7 +2590,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E5">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2627,22 +2598,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F5">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I5">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2653,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2695,57 +2666,57 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>441</v>
+        <v>1790</v>
       </c>
       <c r="C2" s="2">
-        <v>15.95</v>
+        <v>24.18</v>
       </c>
       <c r="D2" s="2">
-        <v>13.25</v>
+        <v>9.67</v>
       </c>
       <c r="E2" s="2">
-        <v>5.87</v>
+        <v>16.45</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>323.45</v>
+        <v>1380</v>
       </c>
       <c r="C3" s="2">
-        <v>30.95</v>
+        <v>24.24</v>
       </c>
       <c r="D3" s="2">
-        <v>4.12</v>
+        <v>4.29</v>
       </c>
       <c r="E3" s="2">
-        <v>0.42</v>
+        <v>11.45</v>
       </c>
       <c r="F3" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G3" s="2">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2753,86 +2724,86 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1197</v>
+        <v>447.4</v>
       </c>
       <c r="C4" s="2">
-        <v>-4.65</v>
+        <v>15.48</v>
       </c>
       <c r="D4" s="2">
-        <v>4.56</v>
+        <v>13.55</v>
       </c>
       <c r="E4" s="2">
-        <v>4.72</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F4" s="2">
         <v>94</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>1259.1</v>
+        <v>325.3</v>
       </c>
       <c r="C5" s="2">
-        <v>0.39</v>
+        <v>35.65</v>
       </c>
       <c r="D5" s="2">
-        <v>2.46</v>
+        <v>2.86</v>
       </c>
       <c r="E5" s="2">
-        <v>1.05</v>
+        <v>-0.47</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H5" s="2">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1">
-        <v>1761</v>
+        <v>1397</v>
       </c>
       <c r="C6" s="2">
-        <v>-1.96</v>
+        <v>8.93</v>
       </c>
       <c r="D6" s="2">
-        <v>5.82</v>
+        <v>-4.15</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.4</v>
+        <v>4.34</v>
       </c>
       <c r="F6" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G6" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="I6" s="2">
-        <v>94</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2840,90 +2811,61 @@
         <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>1216.7</v>
+        <v>2958.7</v>
       </c>
       <c r="C7" s="2">
-        <v>4.25</v>
+        <v>7.56</v>
       </c>
       <c r="D7" s="2">
-        <v>-10.05</v>
+        <v>-4.78</v>
       </c>
       <c r="E7" s="2">
-        <v>0.8</v>
+        <v>4.77</v>
       </c>
       <c r="F7" s="2">
         <v>84</v>
       </c>
       <c r="G7" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="I7" s="2">
-        <v>84</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1">
-        <v>4833</v>
+        <v>1218.8</v>
       </c>
       <c r="C8" s="2">
-        <v>7.11</v>
+        <v>-3.55</v>
       </c>
       <c r="D8" s="2">
-        <v>-7.6</v>
+        <v>4.08</v>
       </c>
       <c r="E8" s="2">
-        <v>-2.26</v>
+        <v>2.85</v>
       </c>
       <c r="F8" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1514.1</v>
-      </c>
-      <c r="C9" s="2">
-        <v>5.51</v>
-      </c>
-      <c r="D9" s="2">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="E9" s="2">
-        <v>-0.77</v>
-      </c>
-      <c r="F9" s="2">
-        <v>80</v>
-      </c>
-      <c r="G9" s="2">
-        <v>92</v>
-      </c>
-      <c r="H9" s="2">
-        <v>80</v>
-      </c>
-      <c r="I9" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2931,7 +2873,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2939,7 +2881,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2947,22 +2889,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2998,13 +2940,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3012,13 +2954,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3026,13 +2968,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2">
         <v>16</v>
-      </c>
-      <c r="D4" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3043,7 +2985,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2">
         <v>34</v>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-10-16</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-10-16</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-10-16</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-10-16</t>
+    <t>Price_2026-10-23</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-10-23</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-10-23</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-10-23</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-10-23</t>
   </si>
   <si>
     <t>RS_Score_2026-10-16</t>
@@ -43,9 +46,6 @@
     <t>RS_Score_2026-10-02</t>
   </si>
   <si>
-    <t>RS_Score_2026-09-25</t>
-  </si>
-  <si>
     <t>TECHM</t>
   </si>
   <si>
@@ -58,135 +58,135 @@
     <t>KOTAKBANK</t>
   </si>
   <si>
+    <t>INFY</t>
+  </si>
+  <si>
     <t>ETERNAL</t>
   </si>
   <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
     <t>ICICIBANK</t>
   </si>
   <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
     <t>TRENT</t>
   </si>
   <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>ONGC</t>
   </si>
   <si>
     <t>COALINDIA</t>
   </si>
   <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
     <t>HDFCBANK</t>
   </si>
   <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>BSE</t>
   </si>
   <si>
     <t>BAJFINANCE</t>
   </si>
   <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
   </si>
   <si>
     <t>TITAN</t>
   </si>
   <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>SBIN</t>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
   </si>
   <si>
     <t>NTPC</t>
   </si>
   <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>ADANIENT</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
   </si>
   <si>
     <t>SHRIRAMFIN</t>
   </si>
   <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>ADANIENT</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
     <t>NESTLEIND</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-10-23</t>
+  </si>
+  <si>
     <t>2026-10-16</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
   </si>
 </sst>
 </file>
@@ -725,25 +725,25 @@
         <v>1790</v>
       </c>
       <c r="C2" s="2">
-        <v>24.18</v>
+        <v>27.99</v>
       </c>
       <c r="D2" s="2">
-        <v>9.67</v>
+        <v>11.06</v>
       </c>
       <c r="E2" s="2">
-        <v>16.45</v>
+        <v>16.97</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>80</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>92</v>
-      </c>
-      <c r="I2" s="2">
-        <v>80</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>2465</v>
+        <v>2530</v>
       </c>
       <c r="C3" s="2">
-        <v>15.68</v>
+        <v>16.3</v>
       </c>
       <c r="D3" s="2">
-        <v>4.43</v>
+        <v>8.25</v>
       </c>
       <c r="E3" s="2">
-        <v>17.72</v>
+        <v>21.87</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>62</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>22</v>
-      </c>
-      <c r="I3" s="2">
-        <v>8</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,25 +786,25 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1380</v>
+        <v>1422.2</v>
       </c>
       <c r="C4" s="2">
-        <v>24.24</v>
+        <v>25.07</v>
       </c>
       <c r="D4" s="2">
-        <v>4.29</v>
+        <v>5.09</v>
       </c>
       <c r="E4" s="2">
-        <v>11.45</v>
+        <v>15.38</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
+        <v>96</v>
+      </c>
+      <c r="H4" s="2">
         <v>84</v>
-      </c>
-      <c r="H4" s="2">
-        <v>86</v>
       </c>
       <c r="I4" s="2">
         <v>86</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>447.4</v>
+        <v>430.5</v>
       </c>
       <c r="C5" s="2">
-        <v>15.48</v>
+        <v>5.74</v>
       </c>
       <c r="D5" s="2">
-        <v>13.55</v>
+        <v>10.24</v>
       </c>
       <c r="E5" s="2">
-        <v>8.460000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>94</v>
+      </c>
+      <c r="H5" s="2">
         <v>100</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>98</v>
-      </c>
-      <c r="I5" s="2">
-        <v>82</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>325.3</v>
+        <v>1153.8</v>
       </c>
       <c r="C6" s="2">
-        <v>35.65</v>
+        <v>0.89</v>
       </c>
       <c r="D6" s="2">
-        <v>2.86</v>
+        <v>-1.9</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.47</v>
+        <v>13.73</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>184.4</v>
+        <v>317.4</v>
       </c>
       <c r="C7" s="2">
-        <v>4.23</v>
+        <v>25.16</v>
       </c>
       <c r="D7" s="2">
-        <v>-0.92</v>
+        <v>1.07</v>
       </c>
       <c r="E7" s="2">
-        <v>10.53</v>
+        <v>-5.39</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="I7" s="2">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1161.2</v>
+        <v>1394.2</v>
       </c>
       <c r="C8" s="2">
-        <v>1.39</v>
+        <v>5.37</v>
       </c>
       <c r="D8" s="2">
-        <v>-0.33</v>
+        <v>-2.62</v>
       </c>
       <c r="E8" s="2">
-        <v>10.44</v>
+        <v>4.47</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="H8" s="2">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1397</v>
+        <v>1892.1</v>
       </c>
       <c r="C9" s="2">
-        <v>8.93</v>
+        <v>3.4</v>
       </c>
       <c r="D9" s="2">
-        <v>-4.15</v>
+        <v>-2.72</v>
       </c>
       <c r="E9" s="2">
-        <v>4.34</v>
+        <v>5.36</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H9" s="2">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I9" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>2958.7</v>
+        <v>1229.5</v>
       </c>
       <c r="C10" s="2">
-        <v>7.56</v>
+        <v>-3.1</v>
       </c>
       <c r="D10" s="2">
-        <v>-4.78</v>
+        <v>2.46</v>
       </c>
       <c r="E10" s="2">
-        <v>4.77</v>
+        <v>2.42</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="I10" s="2">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>1905</v>
+        <v>1217.5</v>
       </c>
       <c r="C11" s="2">
-        <v>8.66</v>
+        <v>-10.78</v>
       </c>
       <c r="D11" s="2">
-        <v>-2.21</v>
+        <v>-1.02</v>
       </c>
       <c r="E11" s="2">
-        <v>0.62</v>
+        <v>2.61</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H11" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1218.8</v>
+        <v>10958</v>
       </c>
       <c r="C12" s="2">
-        <v>-3.55</v>
+        <v>-1.84</v>
       </c>
       <c r="D12" s="2">
-        <v>4.08</v>
+        <v>-7.85</v>
       </c>
       <c r="E12" s="2">
-        <v>2.85</v>
+        <v>-0.89</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="I12" s="2">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1290</v>
+        <v>523.75</v>
       </c>
       <c r="C13" s="2">
-        <v>-1.79</v>
+        <v>-8.49</v>
       </c>
       <c r="D13" s="2">
-        <v>2.71</v>
+        <v>-2.47</v>
       </c>
       <c r="E13" s="2">
-        <v>2.63</v>
+        <v>-0.6</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I13" s="2">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>553</v>
+        <v>2727.5</v>
       </c>
       <c r="C14" s="2">
-        <v>0.99</v>
+        <v>-5.88</v>
       </c>
       <c r="D14" s="2">
-        <v>1.94</v>
+        <v>-8.69</v>
       </c>
       <c r="E14" s="2">
-        <v>0.37</v>
+        <v>1.02</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="I14" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>417.2</v>
+        <v>1702.7</v>
       </c>
       <c r="C15" s="2">
-        <v>-5.07</v>
+        <v>-6.55</v>
       </c>
       <c r="D15" s="2">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="E15" s="2">
-        <v>1.78</v>
+        <v>-4.63</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I15" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>728.85</v>
+        <v>1338</v>
       </c>
       <c r="C16" s="2">
-        <v>-0.8</v>
+        <v>-2.56</v>
       </c>
       <c r="D16" s="2">
-        <v>-0.74</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.29</v>
+        <v>-4.36</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
+        <v>40</v>
+      </c>
+      <c r="H16" s="2">
+        <v>48</v>
+      </c>
+      <c r="I16" s="2">
         <v>76</v>
-      </c>
-      <c r="H16" s="2">
-        <v>84</v>
-      </c>
-      <c r="I16" s="2">
-        <v>68</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1743.2</v>
+        <v>958.6</v>
       </c>
       <c r="C17" s="2">
-        <v>-3.88</v>
+        <v>-5.58</v>
       </c>
       <c r="D17" s="2">
-        <v>2.84</v>
+        <v>-11.4</v>
       </c>
       <c r="E17" s="2">
-        <v>-4.43</v>
+        <v>-2.03</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H17" s="2">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="I17" s="2">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>10862</v>
+        <v>227.5</v>
       </c>
       <c r="C18" s="2">
-        <v>2</v>
+        <v>-7.95</v>
       </c>
       <c r="D18" s="2">
-        <v>-10.05</v>
+        <v>-4.43</v>
       </c>
       <c r="E18" s="2">
-        <v>-1.38</v>
+        <v>-4.81</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="H18" s="2">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="I18" s="2">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>982.1</v>
+        <v>397.45</v>
       </c>
       <c r="C19" s="2">
-        <v>11.77</v>
+        <v>-9.56</v>
       </c>
       <c r="D19" s="2">
-        <v>-14.21</v>
+        <v>-1.67</v>
       </c>
       <c r="E19" s="2">
-        <v>-5.59</v>
+        <v>-5.82</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="I19" s="2">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>263.5</v>
+        <v>1748</v>
       </c>
       <c r="C20" s="2">
-        <v>-7.1</v>
+        <v>-2.67</v>
       </c>
       <c r="D20" s="2">
-        <v>-7.83</v>
+        <v>-10.08</v>
       </c>
       <c r="E20" s="2">
-        <v>0.46</v>
+        <v>-5.51</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I20" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1211.2</v>
+        <v>7084.5</v>
       </c>
       <c r="C21" s="2">
-        <v>-3.78</v>
+        <v>-5.31</v>
       </c>
       <c r="D21" s="2">
-        <v>-8.59</v>
+        <v>-11.98</v>
       </c>
       <c r="E21" s="2">
-        <v>-1.24</v>
+        <v>-3.46</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="H21" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I21" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>4444.8</v>
+        <v>692.8</v>
       </c>
       <c r="C22" s="2">
-        <v>10.32</v>
+        <v>-10.27</v>
       </c>
       <c r="D22" s="2">
-        <v>-11.07</v>
+        <v>-4.97</v>
       </c>
       <c r="E22" s="2">
-        <v>-7.37</v>
+        <v>-4.95</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="H22" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I22" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>7225</v>
+        <v>1190</v>
       </c>
       <c r="C23" s="2">
-        <v>1.12</v>
+        <v>-10.45</v>
       </c>
       <c r="D23" s="2">
-        <v>-9.32</v>
+        <v>-10.46</v>
       </c>
       <c r="E23" s="2">
-        <v>-3.87</v>
+        <v>-2.4</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H23" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I23" s="2">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>4686.9</v>
+        <v>257.9</v>
       </c>
       <c r="C24" s="2">
-        <v>3.58</v>
+        <v>-11.57</v>
       </c>
       <c r="D24" s="2">
-        <v>-11.88</v>
+        <v>-6.61</v>
       </c>
       <c r="E24" s="2">
-        <v>-4.74</v>
+        <v>-3.77</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="H24" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="I24" s="2">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1764</v>
+        <v>1185.5</v>
       </c>
       <c r="C25" s="2">
-        <v>-1</v>
+        <v>-6.43</v>
       </c>
       <c r="D25" s="2">
-        <v>-9.58</v>
+        <v>-6.59</v>
       </c>
       <c r="E25" s="2">
-        <v>-3.99</v>
+        <v>-6.89</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H25" s="2">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="I25" s="2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1216.3</v>
+        <v>3230.8</v>
       </c>
       <c r="C26" s="2">
-        <v>-3.66</v>
+        <v>-22.18</v>
       </c>
       <c r="D26" s="2">
-        <v>-7</v>
+        <v>-8.4</v>
       </c>
       <c r="E26" s="2">
-        <v>-4.65</v>
+        <v>1.48</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="H26" s="2">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I26" s="2">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>376.85</v>
+        <v>928.95</v>
       </c>
       <c r="C27" s="2">
-        <v>-7.59</v>
+        <v>-2.6</v>
       </c>
       <c r="D27" s="2">
-        <v>-5.47</v>
+        <v>-15.1</v>
       </c>
       <c r="E27" s="2">
-        <v>-4.18</v>
+        <v>-5.4</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="H27" s="2">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="I27" s="2">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>962.6</v>
+        <v>959.8</v>
       </c>
       <c r="C28" s="2">
-        <v>-4.05</v>
+        <v>-15.13</v>
       </c>
       <c r="D28" s="2">
-        <v>-11.28</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="E28" s="2">
-        <v>-3.37</v>
+        <v>-2.69</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="H28" s="2">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="I28" s="2">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>315.15</v>
+        <v>1640</v>
       </c>
       <c r="C29" s="2">
-        <v>-9.41</v>
+        <v>-7.22</v>
       </c>
       <c r="D29" s="2">
-        <v>-7.67</v>
+        <v>-10.38</v>
       </c>
       <c r="E29" s="2">
-        <v>-2.63</v>
+        <v>-6.55</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H29" s="2">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="I29" s="2">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>2920.9</v>
+        <v>2861.2</v>
       </c>
       <c r="C30" s="2">
-        <v>-0.03</v>
+        <v>-7.86</v>
       </c>
       <c r="D30" s="2">
-        <v>-14.24</v>
+        <v>-15.94</v>
       </c>
       <c r="E30" s="2">
-        <v>-4.3</v>
+        <v>-4.07</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
+        <v>44</v>
+      </c>
+      <c r="H30" s="2">
         <v>14</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="2">
         <v>24</v>
-      </c>
-      <c r="I30" s="2">
-        <v>22</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>1328</v>
+        <v>10072</v>
       </c>
       <c r="C31" s="2">
-        <v>-3.56</v>
+        <v>1.34</v>
       </c>
       <c r="D31" s="2">
-        <v>-10.09</v>
+        <v>-13.91</v>
       </c>
       <c r="E31" s="2">
-        <v>-4.77</v>
+        <v>-10.14</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="H31" s="2">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="I31" s="2">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>1656.8</v>
+        <v>3647</v>
       </c>
       <c r="C32" s="2">
-        <v>-4.16</v>
+        <v>-12.88</v>
       </c>
       <c r="D32" s="2">
-        <v>-11</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="E32" s="2">
-        <v>-4.29</v>
+        <v>-5.48</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H32" s="2">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="I32" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>1893.8</v>
+        <v>4549</v>
       </c>
       <c r="C33" s="2">
-        <v>-11.82</v>
+        <v>-6.01</v>
       </c>
       <c r="D33" s="2">
-        <v>-8.93</v>
+        <v>-14.7</v>
       </c>
       <c r="E33" s="2">
-        <v>-1.98</v>
+        <v>-6.97</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H33" s="2">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="I33" s="2">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>978.9</v>
+        <v>247.4</v>
       </c>
       <c r="C34" s="2">
-        <v>-11.65</v>
+        <v>-12.83</v>
       </c>
       <c r="D34" s="2">
-        <v>-10.19</v>
+        <v>-7.76</v>
       </c>
       <c r="E34" s="2">
-        <v>-1.72</v>
+        <v>-7.13</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I34" s="2">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>10405</v>
+        <v>362</v>
       </c>
       <c r="C35" s="2">
-        <v>2.57</v>
+        <v>-11.06</v>
       </c>
       <c r="D35" s="2">
-        <v>-10.46</v>
+        <v>-10.65</v>
       </c>
       <c r="E35" s="2">
-        <v>-8.84</v>
+        <v>-7.65</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H35" s="2">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I35" s="2">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>939.95</v>
+        <v>2894</v>
       </c>
       <c r="C36" s="2">
-        <v>5.34</v>
+        <v>-7.56</v>
       </c>
       <c r="D36" s="2">
-        <v>-17.62</v>
+        <v>-12.51</v>
       </c>
       <c r="E36" s="2">
-        <v>-6.94</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="H36" s="2">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I36" s="2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1729</v>
+        <v>1655</v>
       </c>
       <c r="C37" s="2">
-        <v>3.98</v>
+        <v>-7.32</v>
       </c>
       <c r="D37" s="2">
-        <v>-17.11</v>
+        <v>-18.09</v>
       </c>
       <c r="E37" s="2">
-        <v>-6.67</v>
+        <v>-6.09</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2">
+        <v>42</v>
+      </c>
+      <c r="I37" s="2">
         <v>20</v>
-      </c>
-      <c r="I37" s="2">
-        <v>14</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>222</v>
+        <v>4299.7</v>
       </c>
       <c r="C38" s="2">
-        <v>-11.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D38" s="2">
-        <v>-6.25</v>
+        <v>-15.68</v>
       </c>
       <c r="E38" s="2">
-        <v>-4.64</v>
+        <v>-11.03</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="H38" s="2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="I38" s="2">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>175.5</v>
+        <v>2307</v>
       </c>
       <c r="C39" s="2">
-        <v>-10.13</v>
+        <v>-15.32</v>
       </c>
       <c r="D39" s="2">
-        <v>-7.29</v>
+        <v>-15.8</v>
       </c>
       <c r="E39" s="2">
-        <v>-5.41</v>
+        <v>-3.58</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H39" s="2">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="I39" s="2">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>3627.1</v>
+        <v>1814.7</v>
       </c>
       <c r="C40" s="2">
-        <v>-7.41</v>
+        <v>-16.67</v>
       </c>
       <c r="D40" s="2">
-        <v>-10.7</v>
+        <v>-12.04</v>
       </c>
       <c r="E40" s="2">
-        <v>-6.64</v>
+        <v>-6.14</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="H40" s="2">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I40" s="2">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>250.45</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2">
-        <v>-12.39</v>
+        <v>-15.28</v>
       </c>
       <c r="D41" s="2">
-        <v>-7.07</v>
+        <v>-11.26</v>
       </c>
       <c r="E41" s="2">
-        <v>-7.34</v>
+        <v>-8.76</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I41" s="2">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>216.25</v>
+        <v>167.67</v>
       </c>
       <c r="C42" s="2">
-        <v>-5.83</v>
+        <v>-14.45</v>
       </c>
       <c r="D42" s="2">
-        <v>-17.61</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="E42" s="2">
-        <v>-5.93</v>
+        <v>-10.82</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H42" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I42" s="2">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>2885.9</v>
+        <v>11230</v>
       </c>
       <c r="C43" s="2">
-        <v>-5.74</v>
+        <v>-17.15</v>
       </c>
       <c r="D43" s="2">
-        <v>-10.1</v>
+        <v>-19.06</v>
       </c>
       <c r="E43" s="2">
-        <v>-10.07</v>
+        <v>-6.34</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H43" s="2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I43" s="2">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>2331.9</v>
+        <v>7604.5</v>
       </c>
       <c r="C44" s="2">
-        <v>-13.37</v>
+        <v>-9.26</v>
       </c>
       <c r="D44" s="2">
-        <v>-15.36</v>
+        <v>-11.44</v>
       </c>
       <c r="E44" s="2">
-        <v>-4.87</v>
+        <v>-14.45</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H44" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I44" s="2">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,16 +2098,16 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>908</v>
+        <v>2550</v>
       </c>
       <c r="C45" s="2">
-        <v>-12.18</v>
+        <v>-13.37</v>
       </c>
       <c r="D45" s="2">
-        <v>-11.59</v>
+        <v>-14.59</v>
       </c>
       <c r="E45" s="2">
-        <v>-7.96</v>
+        <v>-12.07</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
@@ -2116,10 +2116,10 @@
         <v>10</v>
       </c>
       <c r="H45" s="2">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="I45" s="2">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>2700</v>
+        <v>869.85</v>
       </c>
       <c r="C46" s="2">
-        <v>-7.84</v>
+        <v>-10.99</v>
       </c>
       <c r="D46" s="2">
-        <v>-10.77</v>
+        <v>-19.35</v>
       </c>
       <c r="E46" s="2">
-        <v>-10.6</v>
+        <v>-11.42</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H46" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="I46" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>11445</v>
+        <v>205.03</v>
       </c>
       <c r="C47" s="2">
-        <v>-11.57</v>
+        <v>-15.06</v>
       </c>
       <c r="D47" s="2">
-        <v>-17.9</v>
+        <v>-19.93</v>
       </c>
       <c r="E47" s="2">
-        <v>-5.44</v>
+        <v>-9.76</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H47" s="2">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="I47" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>7890</v>
+        <v>865</v>
       </c>
       <c r="C48" s="2">
-        <v>-6.94</v>
+        <v>-13.51</v>
       </c>
       <c r="D48" s="2">
-        <v>-11.98</v>
+        <v>-22.57</v>
       </c>
       <c r="E48" s="2">
-        <v>-11.79</v>
+        <v>-12.63</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H48" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I48" s="2">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>1265.5</v>
+        <v>1175</v>
       </c>
       <c r="C49" s="2">
-        <v>-11.59</v>
+        <v>-15.17</v>
       </c>
       <c r="D49" s="2">
-        <v>-17.56</v>
+        <v>-22.03</v>
       </c>
       <c r="E49" s="2">
-        <v>-7.79</v>
+        <v>-13.03</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
+        <v>6</v>
+      </c>
+      <c r="H49" s="2">
         <v>58</v>
       </c>
-      <c r="H49" s="2">
+      <c r="I49" s="2">
         <v>32</v>
-      </c>
-      <c r="I49" s="2">
-        <v>30</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,16 +2258,16 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>286.85</v>
+        <v>264.6</v>
       </c>
       <c r="C50" s="2">
-        <v>-24.09</v>
+        <v>-32.22</v>
       </c>
       <c r="D50" s="2">
-        <v>-16.94</v>
+        <v>-22.86</v>
       </c>
       <c r="E50" s="2">
-        <v>-5.58</v>
+        <v>-10.31</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
@@ -2276,7 +2276,7 @@
         <v>4</v>
       </c>
       <c r="H50" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I50" s="2">
         <v>2</v>
@@ -2290,16 +2290,16 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>846</v>
+        <v>815</v>
       </c>
       <c r="C51" s="2">
-        <v>-16.1</v>
+        <v>-20.28</v>
       </c>
       <c r="D51" s="2">
-        <v>-21.11</v>
+        <v>-19.11</v>
       </c>
       <c r="E51" s="2">
-        <v>-19.37</v>
+        <v>-22.08</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
@@ -2308,10 +2308,10 @@
         <v>2</v>
       </c>
       <c r="H51" s="2">
+        <v>2</v>
+      </c>
+      <c r="I51" s="2">
         <v>38</v>
-      </c>
-      <c r="I51" s="2">
-        <v>54</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2465,25 +2465,25 @@
         <v>1790</v>
       </c>
       <c r="C2" s="2">
-        <v>24.18</v>
+        <v>27.99</v>
       </c>
       <c r="D2" s="2">
-        <v>9.67</v>
+        <v>11.06</v>
       </c>
       <c r="E2" s="2">
-        <v>16.45</v>
+        <v>16.97</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>80</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>92</v>
-      </c>
-      <c r="I2" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2491,25 +2491,25 @@
         <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>1380</v>
+        <v>1422.2</v>
       </c>
       <c r="C3" s="2">
-        <v>24.24</v>
+        <v>25.07</v>
       </c>
       <c r="D3" s="2">
-        <v>4.29</v>
+        <v>5.09</v>
       </c>
       <c r="E3" s="2">
-        <v>11.45</v>
+        <v>15.38</v>
       </c>
       <c r="F3" s="2">
         <v>96</v>
       </c>
       <c r="G3" s="2">
+        <v>96</v>
+      </c>
+      <c r="H3" s="2">
         <v>84</v>
-      </c>
-      <c r="H3" s="2">
-        <v>86</v>
       </c>
       <c r="I3" s="2">
         <v>86</v>
@@ -2520,61 +2520,119 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>447.4</v>
+        <v>430.5</v>
       </c>
       <c r="C4" s="2">
-        <v>15.48</v>
+        <v>5.74</v>
       </c>
       <c r="D4" s="2">
-        <v>13.55</v>
+        <v>10.24</v>
       </c>
       <c r="E4" s="2">
-        <v>8.460000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="F4" s="2">
         <v>94</v>
       </c>
       <c r="G4" s="2">
+        <v>94</v>
+      </c>
+      <c r="H4" s="2">
         <v>100</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>98</v>
-      </c>
-      <c r="I4" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>325.3</v>
+        <v>317.4</v>
       </c>
       <c r="C5" s="2">
-        <v>35.65</v>
+        <v>25.16</v>
       </c>
       <c r="D5" s="2">
-        <v>2.86</v>
+        <v>1.07</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.47</v>
+        <v>-5.39</v>
       </c>
       <c r="F5" s="2">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2">
         <v>92</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>98</v>
-      </c>
-      <c r="H5" s="2">
-        <v>100</v>
       </c>
       <c r="I5" s="2">
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1229.5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-3.1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.46</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2.42</v>
+      </c>
+      <c r="F6" s="2">
+        <v>84</v>
+      </c>
+      <c r="G6" s="2">
+        <v>84</v>
+      </c>
+      <c r="H6" s="2">
+        <v>94</v>
+      </c>
+      <c r="I6" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1217.5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-10.78</v>
+      </c>
+      <c r="D7" s="2">
+        <v>-1.02</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2.61</v>
+      </c>
+      <c r="F7" s="2">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" s="2">
+        <v>90</v>
+      </c>
+      <c r="I7" s="2">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2582,7 +2640,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2590,7 +2648,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2598,22 +2656,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2624,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2669,203 +2727,290 @@
         <v>1790</v>
       </c>
       <c r="C2" s="2">
-        <v>24.18</v>
+        <v>27.99</v>
       </c>
       <c r="D2" s="2">
-        <v>9.67</v>
+        <v>11.06</v>
       </c>
       <c r="E2" s="2">
-        <v>16.45</v>
+        <v>16.97</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>80</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>92</v>
-      </c>
-      <c r="I2" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1380</v>
+        <v>2530</v>
       </c>
       <c r="C3" s="2">
-        <v>24.24</v>
+        <v>16.3</v>
       </c>
       <c r="D3" s="2">
-        <v>4.29</v>
+        <v>8.25</v>
       </c>
       <c r="E3" s="2">
-        <v>11.45</v>
+        <v>21.87</v>
       </c>
       <c r="F3" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H3" s="2">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>447.4</v>
+        <v>1422.2</v>
       </c>
       <c r="C4" s="2">
-        <v>15.48</v>
+        <v>25.07</v>
       </c>
       <c r="D4" s="2">
-        <v>13.55</v>
+        <v>5.09</v>
       </c>
       <c r="E4" s="2">
-        <v>8.460000000000001</v>
+        <v>15.38</v>
       </c>
       <c r="F4" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>325.3</v>
+        <v>430.5</v>
       </c>
       <c r="C5" s="2">
-        <v>35.65</v>
+        <v>5.74</v>
       </c>
       <c r="D5" s="2">
-        <v>2.86</v>
+        <v>10.24</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.47</v>
+        <v>6.3</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2">
         <v>100</v>
       </c>
       <c r="I5" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1397</v>
+        <v>1153.8</v>
       </c>
       <c r="C6" s="2">
-        <v>8.93</v>
+        <v>0.89</v>
       </c>
       <c r="D6" s="2">
-        <v>-4.15</v>
+        <v>-1.9</v>
       </c>
       <c r="E6" s="2">
-        <v>4.34</v>
+        <v>13.73</v>
       </c>
       <c r="F6" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="I6" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>2958.7</v>
+        <v>317.4</v>
       </c>
       <c r="C7" s="2">
-        <v>7.56</v>
+        <v>25.16</v>
       </c>
       <c r="D7" s="2">
-        <v>-4.78</v>
+        <v>1.07</v>
       </c>
       <c r="E7" s="2">
-        <v>4.77</v>
+        <v>-5.39</v>
       </c>
       <c r="F7" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2">
         <v>92</v>
       </c>
       <c r="H7" s="2">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="I7" s="2">
-        <v>24</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1218.8</v>
+        <v>1394.2</v>
       </c>
       <c r="C8" s="2">
-        <v>-3.55</v>
+        <v>5.37</v>
       </c>
       <c r="D8" s="2">
-        <v>4.08</v>
+        <v>-2.62</v>
       </c>
       <c r="E8" s="2">
-        <v>2.85</v>
+        <v>4.47</v>
       </c>
       <c r="F8" s="2">
+        <v>88</v>
+      </c>
+      <c r="G8" s="2">
+        <v>88</v>
+      </c>
+      <c r="H8" s="2">
+        <v>86</v>
+      </c>
+      <c r="I8" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1892.1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="D9" s="2">
+        <v>-2.72</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5.36</v>
+      </c>
+      <c r="F9" s="2">
+        <v>86</v>
+      </c>
+      <c r="G9" s="2">
+        <v>82</v>
+      </c>
+      <c r="H9" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1229.5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>-3.1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2.46</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2.42</v>
+      </c>
+      <c r="F10" s="2">
+        <v>84</v>
+      </c>
+      <c r="G10" s="2">
+        <v>84</v>
+      </c>
+      <c r="H10" s="2">
+        <v>94</v>
+      </c>
+      <c r="I10" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1217.5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>-10.78</v>
+      </c>
+      <c r="D11" s="2">
+        <v>-1.02</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2.61</v>
+      </c>
+      <c r="F11" s="2">
+        <v>82</v>
+      </c>
+      <c r="G11" s="2">
         <v>80</v>
       </c>
-      <c r="G8" s="2">
-        <v>94</v>
-      </c>
-      <c r="H8" s="2">
-        <v>94</v>
-      </c>
-      <c r="I8" s="2">
-        <v>72</v>
+      <c r="H11" s="2">
+        <v>90</v>
+      </c>
+      <c r="I11" s="2">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2873,7 +3018,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2881,7 +3026,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2889,22 +3034,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2940,13 +3085,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2954,13 +3099,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2968,13 +3113,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2982,13 +3127,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2">
         <v>16</v>
-      </c>
-      <c r="D5" s="2">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
